--- a/reports/devops-jobs-israel-2026-W43.xlsx
+++ b/reports/devops-jobs-israel-2026-W43.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="497">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-19T12:54:56</t>
+    <t xml:space="preserve">2026-10-20T11:22:55</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -93,6 +93,9 @@
     <t xml:space="preserve">greenhouse</t>
   </si>
   <si>
+    <t xml:space="preserve">lever</t>
+  </si>
+  <si>
     <t xml:space="preserve">Title</t>
   </si>
   <si>
@@ -153,10 +156,13 @@
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4988910101?gh_jid=4988910101</t>
   </si>
   <si>
-    <t xml:space="preserve">Platform Engineering Group Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4983402101?gh_jid=4983402101</t>
+    <t xml:space="preserve">Platform Engineering Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/5010669101?gh_jid=5010669101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-20</t>
   </si>
   <si>
     <t xml:space="preserve">Senior DevOps Engineer</t>
@@ -456,15 +462,42 @@
     <t xml:space="preserve">2026-09-07</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Engineer, DOCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-doca-at-nvidia-4478174885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08</t>
+  </si>
+  <si>
     <t xml:space="preserve">Principal DevOps Engineer (Prisma Browser)</t>
   </si>
   <si>
     <t xml:space="preserve">Palo Alto Networks</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-prisma-browser-at-palo-alto-networks-4469323268</t>
   </si>
   <si>
@@ -483,27 +516,12 @@
     <t xml:space="preserve">2026-10-15</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
     <t xml:space="preserve">Deloitte</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-deloitte-4479294849</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451477598</t>
-  </si>
-  <si>
     <t xml:space="preserve">comblack</t>
   </si>
   <si>
@@ -528,6 +546,12 @@
     <t xml:space="preserve">2026-09-27</t>
   </si>
   <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4469727405</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
   </si>
   <si>
@@ -540,15 +564,6 @@
     <t xml:space="preserve">2026-10-18</t>
   </si>
   <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lod, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moveo-source-4478427154</t>
-  </si>
-  <si>
     <t xml:space="preserve">Claroty</t>
   </si>
   <si>
@@ -558,7 +573,7 @@
     <t xml:space="preserve">Blockaid</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-blockaid-4478435119</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-blockaid-4480236011</t>
   </si>
   <si>
     <t xml:space="preserve">Transmit Security</t>
@@ -579,763 +594,808 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-comblack-4480971929</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4477992588</t>
+    <t xml:space="preserve">Senior DevOps Engineer-5692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">entrypoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-5692-at-entrypoint-4478139921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARAN Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aran-software-4479824052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4478465745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cellebrite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4479674975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-check-point-software-4479304749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4479116905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Base44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-base44-at-base44-4474179911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-calanit-by-one-4480898845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4476644367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-compie-technologies-4481531841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4480868969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SeeTrue AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-devops-engineer-at-seetrue-ai-4477069152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gness-4479919415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps &amp; AI Enablement Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xsight Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-ai-enablement-engineer-at-xsight-labs-4471491552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AllCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4470273860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer לארגון פיננסי מוביל במרכז הארץ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%D7%9C%D7%90%D7%A8%D7%92%D7%95%D7%9F-%D7%A4%D7%99%D7%A0%D7%A0%D7%A1%D7%99-%D7%9E%D7%95%D7%91%D7%99%D7%9C-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%90%D7%A8%D7%A5-at-jobist-4477738635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integress, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-integress-inc-4479934720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4478251445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4478276676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4480957726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-controp-precision-technologies-ltd-4479972286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-site-reliability-engineer-at-palo-alto-networks-4470801230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops / SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIQAI Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-sre-at-uniqai-systems-4478231249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-confidential-careers-4476662621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE / Linux Performance Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pacaya HR Experts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-linux-performance-engineer-at-pacaya-hr-experts-4479930422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4478209649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARMAN International</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pacaya-hr-experts-4479924948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Engineer (Infra Platform)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-infra-platform-at-monday-com-4479587116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Full Stack Engineer – DevOps &amp; Cloud Focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sheba Medical Center, Tel Hashomer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-full-stack-engineer-%E2%80%93-devops-cloud-focus-at-sheba-medical-center-tel-hashomer-4478671787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-jobgether-4480437632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps &amp; Cloud Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-cloud-infrastructure-at-nimble-4450219176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-at-lendbuzz-4477980904</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-13</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevOps Engineer-5692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">entrypoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-5692-at-entrypoint-4478139921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - AI for Security Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lenovo</t>
+    <t xml:space="preserve">Application Infrastructure Engineer (1006977)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-1006977-at-elad-software-systems-4481553636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software developer and DevOps engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysBind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-developer-and-devops-engineer-at-sysbind-4478663562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer, NCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-4453261687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4476601079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infra Engineer Team Lead - IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ScaleOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-team-lead-il-at-scaleops-4479538658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Technical Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-technical-lead-at-pacaya-hr-experts-4479930327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Security Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Security</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-for-security-team-at-lenovo-4477907387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARAN Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aran-software-4479824052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4478465745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cellebrite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4479674975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-check-point-software-4479304749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4479116905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Base44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-base44-at-base44-4474179911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-calanit-by-one-4480898845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer — Cybersecurity business unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-%E2%80%94-cybersecurity-business-unit-at-drivenets-4477987658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4476644367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Technical Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fig Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-technical-lead-at-fig-security-4475988067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - AI Security Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-ai-security-team-at-lenovo-4477578131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4480868969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SeeTrue AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-devops-engineer-at-seetrue-ai-4477069152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gness-4479919415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps &amp; AI Enablement Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xsight Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-ai-enablement-engineer-at-xsight-labs-4471491552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AllCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4470273860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integress, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-integress-inc-4479934720</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4478251445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4478276676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4480957726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-controp-precision-technologies-ltd-4479972286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-site-reliability-engineer-at-palo-alto-networks-4470801230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops / SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIQAI Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-sre-at-uniqai-systems-4478231249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-confidential-careers-4476662621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE / Linux Performance Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pacaya HR Experts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-linux-performance-engineer-at-pacaya-hr-experts-4479930422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4478209649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARMAN International</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Edge Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-edge-team-at-lenovo-4477910328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pacaya-hr-experts-4479924948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer, Graviton Team</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-security-engineer-at-confidential-careers-4478210872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead &amp; Cloud Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yanolja Go Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-cloud-architect-at-yanolja-go-global-4476647765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (37823)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-37823-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4480979267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4477094134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Administrator - position no. 1768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBI Investment House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-position-no-1768-at-ibi-investment-house-4478254402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4481565145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (37562)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-37562-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4480965834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mendix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boston, MA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://jobs.lever.co/mendix/f61ca692-a66b-4e9f-a864-ad29e7cd716e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=8264438&amp;gh_jid=8264438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux &amp; HPC Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novocure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirat HaCarmel, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-novocure-4478872342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Integration Student, SPIV team</t>
   </si>
   <si>
     <t xml:space="preserve">Amazon</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-graviton-team-at-amazon-4478568501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Engineer (Infra Platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-infra-platform-at-monday-com-4479587116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps &amp; Cloud Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-cloud-infrastructure-at-nimble-4450219176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-at-lendbuzz-4477980904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer - AI Security Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-ai-security-team-at-lenovo-4477568550</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer, NCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-4453261687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4476601079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infra Engineer Team Lead - IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScaleOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-team-lead-il-at-scaleops-4479538658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4478103033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer #8106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tesnet Group Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%238106-at-tesnet-group-ltd-4478384662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-technical-lead-at-pacaya-hr-experts-4479930327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-security-engineer-at-confidential-careers-4478210872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (37823)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-37823-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4480979267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4477094134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Administrator - position no. 1768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBI Investment House</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-position-no-1768-at-ibi-investment-house-4478254402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INGIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4476707352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (37562)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-37562-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4480965834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux &amp; HPC Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novocure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tirat HaCarmel, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-novocure-4478872342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-4456348779</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-student-spiv-team-at-amazon-4456348779</t>
   </si>
   <si>
     <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
@@ -1365,27 +1425,12 @@
     <t xml:space="preserve">2026-09-04</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-abra-4467537853</t>
-  </si>
-  <si>
     <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
   </si>
   <si>
     <t xml:space="preserve">Kela Technologies</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
   </si>
   <si>
@@ -1404,21 +1449,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
   </si>
   <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cye-4477476916</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
   </si>
   <si>
@@ -1471,9 +1501,6 @@
   </si>
   <si>
     <t xml:space="preserve">indeed_il</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lever</t>
   </si>
   <si>
     <t xml:space="preserve">alljobs</t>
@@ -1607,7 +1634,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7">
@@ -1615,7 +1642,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -1623,7 +1650,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -1631,7 +1658,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>859</v>
+        <v>848</v>
       </c>
     </row>
     <row r="10">
@@ -1703,7 +1730,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
@@ -1712,6 +1739,14 @@
       </c>
       <c r="B20" s="3">
         <v>25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1727,31 +1762,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="B2" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="B3" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>454</v>
+        <v>392</v>
       </c>
       <c r="B4" s="3">
         <v>8</v>
@@ -1759,7 +1794,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -1767,7 +1802,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -1775,7 +1810,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1794,15 +1829,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="B2" s="3">
         <v>29</v>
@@ -1810,15 +1845,15 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="B3" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="B4" s="3">
         <v>24</v>
@@ -1826,7 +1861,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B5" s="3">
         <v>23</v>
@@ -1834,63 +1869,63 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>476</v>
+        <v>281</v>
       </c>
       <c r="B6" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>277</v>
+        <v>486</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>477</v>
+        <v>377</v>
       </c>
       <c r="B8" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>363</v>
+        <v>487</v>
       </c>
       <c r="B9" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="B13" s="3">
         <v>11</v>
@@ -1898,7 +1933,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="B14" s="3">
         <v>11</v>
@@ -1906,7 +1941,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>359</v>
+        <v>488</v>
       </c>
       <c r="B15" s="3">
         <v>8</v>
@@ -1914,10 +1949,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>478</v>
+        <v>372</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1942,13 +1977,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2">
@@ -1959,10 +1994,10 @@
         <v>25</v>
       </c>
       <c r="C2" s="3">
-        <v>12.8</v>
+        <v>12.2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1974,85 +2009,85 @@
         <v>72</v>
       </c>
       <c r="C3" s="3">
-        <v>37.3</v>
+        <v>54.7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>484</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>36.7</v>
+        <v>31.5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>18.8</v>
+        <v>14.1</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>24.9</v>
+        <v>19.6</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2077,1421 +2112,1419 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J3" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="J4" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J5" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="J6" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J7" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J8" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J9" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J10" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J11" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J12" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J13" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J14" s="3">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J15" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J16" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="J17" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J18" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J19" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J20" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J21" s="3">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="J22" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J23" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J24" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J25" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J26" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J27" s="3">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>46</v>
+        <v>152</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J28" s="3">
-        <v>4</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="D29" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J29" s="3">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>51</v>
+        <v>164</v>
       </c>
       <c r="J30" s="3">
-        <v>69</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>163</v>
+        <v>50</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="J31" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>48</v>
+        <v>169</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J32" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J33" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="D34" s="3" t="s">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J34" s="3">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="D35" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="J35" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>46</v>
+        <v>152</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="J36" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>182</v>
+        <v>47</v>
       </c>
       <c r="J37" s="3">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>184</v>
+        <v>154</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="J38" s="3">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="J39" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="J40" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>194</v>
+        <v>152</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>195</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>147</v>
+        <v>196</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>48</v>
+        <v>197</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>196</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="J41" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="D42" s="3" t="s">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="J42" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="D43" s="3" t="s">
-        <v>48</v>
+        <v>203</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="J43" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>205</v>
+        <v>154</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>206</v>
+        <v>50</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>172</v>
-      </c>
       <c r="J44" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>208</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>147</v>
+        <v>209</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="J45" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>46</v>
+        <v>211</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
@@ -3501,27 +3534,27 @@
         <v>213</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="J46" s="3">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>214</v>
+        <v>152</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>215</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
@@ -3531,57 +3564,57 @@
         <v>216</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>217</v>
+        <v>171</v>
       </c>
       <c r="J47" s="3">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="D48" s="3" t="s">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="I48" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>187</v>
-      </c>
       <c r="C49" s="3" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
@@ -3591,7 +3624,7 @@
         <v>221</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>189</v>
+        <v>151</v>
       </c>
       <c r="J49" s="3">
         <v>6</v>
@@ -3599,511 +3632,509 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>222</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>184</v>
+        <v>223</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>127</v>
+        <v>224</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>158</v>
+        <v>47</v>
       </c>
       <c r="J50" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>224</v>
+        <v>48</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>147</v>
+        <v>227</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>227</v>
+        <v>180</v>
       </c>
       <c r="J51" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>196</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="J52" s="3">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>46</v>
+        <v>232</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>231</v>
+        <v>149</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="J53" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>233</v>
+        <v>152</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>59</v>
+        <v>180</v>
       </c>
       <c r="J54" s="3">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>156</v>
+        <v>227</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="J55" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>156</v>
+        <v>241</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>172</v>
+        <v>243</v>
       </c>
       <c r="J56" s="3">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>231</v>
+        <v>154</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="J57" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>247</v>
+        <v>171</v>
       </c>
       <c r="J58" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>154</v>
+        <v>249</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>245</v>
+        <v>196</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>36</v>
+        <v>197</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>165</v>
+        <v>252</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>63</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>250</v>
+        <v>152</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>199</v>
+        <v>149</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>253</v>
+        <v>171</v>
       </c>
       <c r="J60" s="3">
-        <v>62</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>154</v>
+        <v>42</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>156</v>
+        <v>260</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J63" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>41</v>
+        <v>262</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>261</v>
+        <v>154</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>165</v>
+        <v>53</v>
       </c>
       <c r="J64" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>76</v>
+        <v>265</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>263</v>
+        <v>158</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>265</v>
+        <v>156</v>
       </c>
       <c r="J65" s="3">
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>266</v>
+        <v>78</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>146</v>
+        <v>267</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>168</v>
+        <v>269</v>
       </c>
       <c r="J66" s="3">
         <v>22</v>
@@ -4111,49 +4142,49 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>269</v>
+        <v>158</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="J67" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>273</v>
+        <v>209</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
@@ -4163,10 +4194,10 @@
         <v>274</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="J68" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4177,17 +4208,15 @@
         <v>276</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>184</v>
+        <v>277</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>127</v>
+        <v>197</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>277</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
@@ -4195,10 +4224,10 @@
         <v>278</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J69" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
@@ -4209,23 +4238,25 @@
         <v>280</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F70" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>281</v>
+      </c>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J70" s="3">
         <v>1</v>
@@ -4233,49 +4264,49 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>159</v>
+        <v>284</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>71</v>
+        <v>180</v>
       </c>
       <c r="J71" s="3">
-        <v>60</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>285</v>
+        <v>148</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>286</v>
+        <v>149</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
@@ -4285,281 +4316,279 @@
         <v>287</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>288</v>
+        <v>73</v>
       </c>
       <c r="J72" s="3">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>195</v>
-      </c>
       <c r="C73" s="3" t="s">
-        <v>147</v>
+        <v>290</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>189</v>
+        <v>292</v>
       </c>
       <c r="J73" s="3">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J74" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>273</v>
+        <v>149</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F75" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>296</v>
+      </c>
       <c r="G75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>189</v>
+        <v>66</v>
       </c>
       <c r="J75" s="3">
-        <v>6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>296</v>
+        <v>263</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>297</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>64</v>
+        <v>164</v>
       </c>
       <c r="J76" s="3">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>147</v>
+        <v>209</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>153</v>
+        <v>47</v>
       </c>
       <c r="J77" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>147</v>
+        <v>305</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>168</v>
+        <v>47</v>
       </c>
       <c r="J78" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>146</v>
+        <v>308</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>307</v>
+        <v>174</v>
       </c>
       <c r="J79" s="3">
-        <v>46</v>
+        <v>23</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>309</v>
+        <v>158</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>189</v>
+        <v>312</v>
       </c>
       <c r="J80" s="3">
-        <v>6</v>
+        <v>47</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>195</v>
+        <v>314</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>196</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>114</v>
+        <v>316</v>
       </c>
       <c r="J81" s="3">
         <v>7</v>
@@ -4567,430 +4596,488 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>212</v>
+        <v>149</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>316</v>
+        <v>47</v>
       </c>
       <c r="J82" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>159</v>
+        <v>321</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="J83" s="3">
-        <v>66</v>
+        <v>14</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>200</v>
+        <v>129</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>153</v>
+        <v>47</v>
       </c>
       <c r="J84" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>251</v>
+        <v>148</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>199</v>
+        <v>241</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>324</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="J85" s="3">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>147</v>
+        <v>332</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>48</v>
+        <v>197</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="J86" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>187</v>
+        <v>335</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>245</v>
+        <v>154</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="J87" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="J88" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>224</v>
+        <v>339</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>276</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F89" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>340</v>
+      </c>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>272</v>
+        <v>343</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>184</v>
+        <v>344</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>196</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="J90" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>342</v>
+        <v>217</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>210</v>
+        <v>61</v>
       </c>
       <c r="J92" s="3">
-        <v>3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="J93" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>102</v>
+        <v>171</v>
       </c>
       <c r="J94" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>165</v>
+        <v>47</v>
       </c>
       <c r="J95" s="3">
         <v>0</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="J96" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="J97" s="3">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J95"/>
+  <autoFilter ref="A1:J97"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5086,6 +5173,8 @@
     <hyperlink ref="H93" r:id="rId92"/>
     <hyperlink ref="H94" r:id="rId93"/>
     <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5093,9 +5182,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="49" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="1" max="1" width="51" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5104,55 +5193,55 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>154</v>
+        <v>45</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>161</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>162</v>
+        <v>36</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>164</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>147</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5160,18 +5249,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>161</v>
+        <v>222</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>184</v>
+        <v>223</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5179,18 +5268,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>185</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>154</v>
+        <v>300</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>218</v>
+        <v>301</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5198,18 +5287,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>219</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>154</v>
+        <v>303</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>248</v>
+        <v>304</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>245</v>
+        <v>305</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5217,18 +5306,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>249</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>154</v>
+        <v>317</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>254</v>
+        <v>318</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5236,18 +5325,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>255</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>154</v>
+        <v>324</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>184</v>
+        <v>326</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5255,18 +5344,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>257</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>154</v>
+        <v>357</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>258</v>
+        <v>358</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5274,163 +5363,11 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:G9"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5440,14 +5377,6 @@
     <hyperlink ref="G7" r:id="rId6"/>
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
-    <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5461,15 +5390,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B2" s="3">
         <v>19</v>
@@ -5477,31 +5406,31 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>196</v>
+        <v>368</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="B4" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="B5" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="B6" s="3">
         <v>11</v>
@@ -5509,7 +5438,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="B7" s="3">
         <v>10</v>
@@ -5517,7 +5446,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B8" s="3">
         <v>10</v>
@@ -5525,7 +5454,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="B9" s="3">
         <v>10</v>
@@ -5533,15 +5462,15 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B11" s="3">
         <v>9</v>
@@ -5549,7 +5478,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="B12" s="3">
         <v>8</v>
@@ -5557,7 +5486,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
@@ -5565,7 +5494,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
@@ -5573,7 +5502,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -5581,7 +5510,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5600,15 +5529,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B2" s="3">
         <v>5</v>
@@ -5616,15 +5545,15 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>81</v>
+        <v>158</v>
       </c>
       <c r="B3" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>146</v>
+        <v>83</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -5632,15 +5561,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>195</v>
+        <v>35</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5648,7 +5577,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>98</v>
+        <v>148</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5656,7 +5585,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>159</v>
+        <v>280</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5664,23 +5593,23 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>187</v>
+        <v>49</v>
       </c>
       <c r="B9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>276</v>
+        <v>118</v>
       </c>
       <c r="B10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>47</v>
+        <v>167</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5688,7 +5617,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>116</v>
+        <v>217</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5696,7 +5625,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>161</v>
+        <v>263</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5704,7 +5633,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5712,7 +5641,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>272</v>
+        <v>347</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5720,10 +5649,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>339</v>
+        <v>57</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5741,16 +5670,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2">
@@ -5758,7 +5687,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3">
         <v>19.0</v>
@@ -5772,7 +5701,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3">
         <v>18.6</v>
@@ -5786,7 +5715,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C4" s="3">
         <v>9.2</v>
@@ -5800,7 +5729,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C5" s="3">
         <v>7.1</v>
@@ -5814,13 +5743,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>195</v>
+        <v>49</v>
       </c>
       <c r="C6" s="3">
-        <v>6.2</v>
+        <v>6.0</v>
       </c>
       <c r="D6" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -5828,13 +5757,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="C7" s="3">
         <v>6.0</v>
       </c>
       <c r="D7" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -5842,13 +5771,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>146</v>
+        <v>280</v>
       </c>
       <c r="C8" s="3">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="D8" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -5856,10 +5785,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>276</v>
+        <v>148</v>
       </c>
       <c r="C9" s="3">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="D9" s="3">
         <v>3</v>
@@ -5870,13 +5799,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>187</v>
+        <v>118</v>
       </c>
       <c r="C10" s="3">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5884,10 +5813,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>116</v>
+        <v>276</v>
       </c>
       <c r="C11" s="3">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="D11" s="3">
         <v>2</v>
@@ -5898,13 +5827,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>159</v>
+        <v>57</v>
       </c>
       <c r="C12" s="3">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="D12" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -5912,13 +5841,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>272</v>
+        <v>133</v>
       </c>
       <c r="C13" s="3">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -5926,13 +5855,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>55</v>
+        <v>167</v>
       </c>
       <c r="C14" s="3">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -5940,10 +5869,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>251</v>
+        <v>217</v>
       </c>
       <c r="C15" s="3">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -5954,13 +5883,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>131</v>
+        <v>263</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
       </c>
       <c r="D16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5977,46 +5906,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -6032,47 +5961,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B2" s="3">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B5" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -6080,7 +6009,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -6088,9 +6017,17 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -6115,34 +6052,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -6150,31 +6087,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>378</v>
+        <v>57</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>379</v>
+        <v>58</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>383</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3">
@@ -6182,31 +6119,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>147</v>
+        <v>397</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4">
@@ -6214,31 +6151,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>245</v>
+        <v>154</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>71</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5">
@@ -6246,31 +6183,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>147</v>
+        <v>241</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6">
@@ -6278,31 +6215,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>401</v>
+        <v>154</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="F6" s="3">
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>153</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
@@ -6310,31 +6247,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>147</v>
+        <v>419</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="F7" s="3">
         <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>408</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8">
@@ -6342,31 +6279,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>409</v>
+        <v>349</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>410</v>
+        <v>154</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="F8" s="3">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>412</v>
+        <v>350</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9">
@@ -6374,31 +6311,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>415</v>
+        <v>215</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="F9" s="3">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
     </row>
     <row r="10">
@@ -6406,31 +6343,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>162</v>
+        <v>431</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>380</v>
+        <v>432</v>
       </c>
       <c r="F10" s="3">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>189</v>
+        <v>435</v>
       </c>
     </row>
     <row r="11">
@@ -6438,31 +6375,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>212</v>
+        <v>168</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F11" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>102</v>
+        <v>316</v>
       </c>
     </row>
     <row r="12">
@@ -6470,31 +6407,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>430</v>
+        <v>148</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>147</v>
+        <v>441</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="F12" s="3">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>253</v>
+        <v>423</v>
       </c>
     </row>
     <row r="13">
@@ -6502,31 +6439,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="F13" s="3">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>408</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14">
@@ -6534,31 +6471,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>293</v>
+        <v>449</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>273</v>
+        <v>154</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F14" s="3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>438</v>
+        <v>451</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>71</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15">
@@ -6566,31 +6503,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>391</v>
+        <v>445</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="F15" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>129</v>
+        <v>423</v>
       </c>
     </row>
     <row r="16">
@@ -6598,31 +6535,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>444</v>
+        <v>277</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="F16" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>447</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6630,31 +6567,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>449</v>
+        <v>409</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>184</v>
+        <v>241</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="F17" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>210</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18">
@@ -6662,31 +6599,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>147</v>
+        <v>464</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>454</v>
+        <v>398</v>
       </c>
       <c r="F18" s="3">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>64</v>
+        <v>467</v>
       </c>
     </row>
     <row r="19">
@@ -6694,31 +6631,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>417</v>
+        <v>392</v>
       </c>
       <c r="F19" s="3">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20">
@@ -6726,31 +6663,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>463</v>
+        <v>196</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>454</v>
+        <v>432</v>
       </c>
       <c r="F20" s="3">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>227</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21">
@@ -6758,31 +6695,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="F21" s="3">
         <v>46</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W43.xlsx
+++ b/reports/devops-jobs-israel-2026-W43.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="487">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-20T11:22:55</t>
+    <t xml:space="preserve">2026-10-21T11:38:03</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -222,15 +222,6 @@
     <t xml:space="preserve">2026-08-31</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4700779006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-23</t>
-  </si>
-  <si>
     <t xml:space="preserve">Senior DevSecOps Manager</t>
   </si>
   <si>
@@ -255,1047 +246,1011 @@
     <t xml:space="preserve">2026-08-27</t>
   </si>
   <si>
+    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer, Traffic Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Istio, Service Mesh, Nginx, Networking, Observability, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8200807?gh_jid=8200807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Developer – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Docker, Linux, Prometheus, Grafana, MySQL, Redis, Kafka, Observability, Airflow, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8176684?gh_jid=8176684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/8264120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior IT Infrastructure Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8882905002?gh_jid=8882905002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yotpo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Engineer - Office of the CTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8211515?gh_jid=8211515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8873995002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orcasecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer- Edge Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saltsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, Docker, CI/CD, Helm, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://salt.security/job-board?gh_jid=5208152007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (Prisma Browser)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-prisma-browser-at-palo-alto-networks-4469323268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-priority-software-4477000056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451477598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fullpath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fullpath-4480776925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4480982357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Backend Infrastructure Team (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-infrastructure-team-cortex-at-palo-alto-networks-4470803159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4469727405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4480881694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At-Bay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-at-bay-4471503422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4478219818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blockaid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-blockaid-4480236011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-comblack-4480971929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARAN Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aran-software-4479824052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4478465745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4480488912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-check-point-software-4479304749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cellebrite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4479674975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4479116905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4480795007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4478985380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4480868969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SeeTrue AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-devops-engineer-at-seetrue-ai-4477069152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps &amp; AI Enablement Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xsight Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-ai-enablement-engineer-at-xsight-labs-4471491552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AllCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4470273860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer לארגון פיננסי מוביל במרכז הארץ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%D7%9C%D7%90%D7%A8%D7%92%D7%95%D7%9F-%D7%A4%D7%99%D7%A0%D7%A0%D7%A1%D7%99-%D7%9E%D7%95%D7%91%D7%99%D7%9C-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%90%D7%A8%D7%A5-at-jobist-4477738635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integress, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-integress-inc-4479934720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4478251445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4478276676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4482049895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-controp-precision-technologies-ltd-4479972286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application DevOps Engineer (1006977)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-devops-engineer-1006977-at-elad-software-systems-4481553636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Technical Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pacaya HR Experts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-technical-lead-at-pacaya-hr-experts-4479930327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops / SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIQAI Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-sre-at-uniqai-systems-4478231249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior SRE Engineer /Senior DevOps</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer, Traffic Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Istio, Service Mesh, Nginx, Networking, Observability, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8200807?gh_jid=8200807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Developer – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Docker, Linux, Prometheus, Grafana, MySQL, Redis, Kafka, Observability, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8176684?gh_jid=8176684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/8264120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior IT Infrastructure Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8882905002?gh_jid=8882905002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yotpo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Engineer - Office of the CTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8211515?gh_jid=8211515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8873995002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orcasecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer- Edge Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saltsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Docker, CI/CD, Helm, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://salt.security/job-board?gh_jid=5208152007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer, DOCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-doca-at-nvidia-4478174885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer (Prisma Browser)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-prisma-browser-at-palo-alto-networks-4469323268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-priority-software-4477000056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deloitte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-deloitte-4479294849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4480982357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - Backend Infrastructure Team (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-infrastructure-team-cortex-at-palo-alto-networks-4470803159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4469727405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4480881694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4478219818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blockaid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-blockaid-4480236011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-comblack-4480971929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer-5692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">entrypoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-5692-at-entrypoint-4478139921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARAN Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aran-software-4479824052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4478465745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cellebrite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4479674975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-check-point-software-4479304749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4479116905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Base44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-base44-at-base44-4474179911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-01</t>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-site-reliability-engineer-at-palo-alto-networks-4470801230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-confidential-careers-4476662621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4478209649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pacaya-hr-experts-4479924948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Engineer (Infra Platform)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-infra-platform-at-monday-com-4479587116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Full Stack Engineer – DevOps &amp; Cloud Focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sheba Medical Center, Tel Hashomer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-full-stack-engineer-%E2%80%93-devops-cloud-focus-at-sheba-medical-center-tel-hashomer-4478671787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-jobgether-4480437632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps &amp; Cloud Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-cloud-infrastructure-at-nimble-4450219176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-at-lendbuzz-4477980904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer - AI Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-ai-platforms-at-palo-alto-networks-4471749164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guesty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-guesty-4473205757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software developer and DevOps engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysBind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-developer-and-devops-engineer-at-sysbind-4478663562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Engineer (GCP Focus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MyOps by Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-gcp-focus-at-myops-by-yael-group-4478218206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infra Engineer Team Lead - IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ScaleOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-team-lead-il-at-scaleops-4479538658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Infrastructure Engineer (1007969)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-1007969-at-elad-software-systems-4482089049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-at-moveo-source-4480775799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (37823)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-37823-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4480979267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer, NCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-4453269633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4478983773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer (10296)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bynet Data Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-10296-at-bynet-data-communications-4478972863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Administrator - position no. 1768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBI Investment House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-position-no-1768-at-ibi-investment-house-4478254402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4481565145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (37562)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-37562-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4480965834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mendix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boston, MA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://jobs.lever.co/mendix/f61ca692-a66b-4e9f-a864-ad29e7cd716e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=8264438&amp;gh_jid=8264438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux &amp; HPC Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novocure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirat HaCarmel, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-novocure-4478872342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
   </si>
   <si>
     <t xml:space="preserve">Calanit by one</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-calanit-by-one-4480898845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4476644367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-compie-technologies-4481531841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4480868969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SeeTrue AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-devops-engineer-at-seetrue-ai-4477069152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gness-4479919415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps &amp; AI Enablement Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xsight Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-ai-enablement-engineer-at-xsight-labs-4471491552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AllCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4470273860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer לארגון פיננסי מוביל במרכז הארץ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%D7%9C%D7%90%D7%A8%D7%92%D7%95%D7%9F-%D7%A4%D7%99%D7%A0%D7%A0%D7%A1%D7%99-%D7%9E%D7%95%D7%91%D7%99%D7%9C-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%90%D7%A8%D7%A5-at-jobist-4477738635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integress, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-integress-inc-4479934720</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4478251445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4478276676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4480957726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-controp-precision-technologies-ltd-4479972286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-site-reliability-engineer-at-palo-alto-networks-4470801230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops / SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIQAI Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-sre-at-uniqai-systems-4478231249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-confidential-careers-4476662621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE / Linux Performance Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pacaya HR Experts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-linux-performance-engineer-at-pacaya-hr-experts-4479930422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4478209649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARMAN International</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pacaya-hr-experts-4479924948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Engineer (Infra Platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-infra-platform-at-monday-com-4479587116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Full Stack Engineer – DevOps &amp; Cloud Focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sheba Medical Center, Tel Hashomer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-full-stack-engineer-%E2%80%93-devops-cloud-focus-at-sheba-medical-center-tel-hashomer-4478671787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-jobgether-4480437632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps &amp; Cloud Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-cloud-infrastructure-at-nimble-4450219176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-at-lendbuzz-4477980904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application Infrastructure Engineer (1006977)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-1006977-at-elad-software-systems-4481553636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software developer and DevOps engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysBind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-developer-and-devops-engineer-at-sysbind-4478663562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer, NCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-4453261687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4476601079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infra Engineer Team Lead - IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScaleOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-team-lead-il-at-scaleops-4479538658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Technical Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-technical-lead-at-pacaya-hr-experts-4479930327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-security-engineer-at-confidential-careers-4478210872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead &amp; Cloud Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yanolja Go Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-cloud-architect-at-yanolja-go-global-4476647765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (37823)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-37823-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4480979267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4477094134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Administrator - position no. 1768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBI Investment House</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-position-no-1768-at-ibi-investment-house-4478254402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INGIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4481565145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (37562)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-37562-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4480965834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mendix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boston, MA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://jobs.lever.co/mendix/f61ca692-a66b-4e9f-a864-ad29e7cd716e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=8264438&amp;gh_jid=8264438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux &amp; HPC Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novocure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tirat HaCarmel, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-novocure-4478872342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
     <t xml:space="preserve">North District, Israel</t>
   </si>
   <si>
@@ -1375,6 +1330,21 @@
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New York City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7995568003</t>
   </si>
   <si>
     <t xml:space="preserve">Security Analyst (Student Position)</t>
@@ -1634,7 +1604,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
@@ -1642,7 +1612,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -1650,7 +1620,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
@@ -1658,7 +1628,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="10">
@@ -1730,7 +1700,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
@@ -1738,7 +1708,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -1765,28 +1735,28 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="B2" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>410</v>
+        <v>378</v>
       </c>
       <c r="B3" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B4" s="3">
         <v>8</v>
@@ -1794,7 +1764,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -1802,7 +1772,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -1810,7 +1780,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1829,39 +1799,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B2" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="B4" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="B5" s="3">
         <v>23</v>
@@ -1869,55 +1839,55 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>281</v>
+        <v>361</v>
       </c>
       <c r="B6" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>486</v>
+        <v>363</v>
       </c>
       <c r="B7" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>377</v>
+        <v>476</v>
       </c>
       <c r="B8" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="B9" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="B12" s="3">
         <v>12</v>
@@ -1925,7 +1895,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="B13" s="3">
         <v>11</v>
@@ -1933,15 +1903,15 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="B14" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="B15" s="3">
         <v>8</v>
@@ -1949,7 +1919,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>372</v>
+        <v>314</v>
       </c>
       <c r="B16" s="3">
         <v>8</v>
@@ -1977,13 +1947,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
     </row>
     <row r="2">
@@ -1991,13 +1961,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3">
-        <v>12.2</v>
+        <v>11.3</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2009,25 +1979,25 @@
         <v>72</v>
       </c>
       <c r="C3" s="3">
-        <v>54.7</v>
+        <v>38.5</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="E4" s="3"/>
     </row>
@@ -2039,55 +2009,55 @@
         <v>1</v>
       </c>
       <c r="C5" s="3">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>31.5</v>
+        <v>28.8</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>14.1</v>
+        <v>14.9</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2100,7 +2070,7 @@
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2171,7 +2141,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -2203,7 +2173,7 @@
         <v>41</v>
       </c>
       <c r="J3" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -2235,7 +2205,7 @@
         <v>47</v>
       </c>
       <c r="J4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -2267,7 +2237,7 @@
         <v>53</v>
       </c>
       <c r="J5" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6">
@@ -2299,7 +2269,7 @@
         <v>53</v>
       </c>
       <c r="J6" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -2331,7 +2301,7 @@
         <v>61</v>
       </c>
       <c r="J7" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
@@ -2363,12 +2333,12 @@
         <v>66</v>
       </c>
       <c r="J8" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>63</v>
@@ -2383,24 +2353,24 @@
         <v>43</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J9" s="3">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>63</v>
@@ -2415,30 +2385,30 @@
         <v>43</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J10" s="3">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>50</v>
@@ -2447,30 +2417,30 @@
         <v>43</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J11" s="3">
-        <v>54</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>50</v>
@@ -2479,94 +2449,94 @@
         <v>43</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J12" s="3">
-        <v>36</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J13" s="3">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J14" s="3">
-        <v>85</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>50</v>
@@ -2575,68 +2545,68 @@
         <v>38</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="J15" s="3">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="J16" s="3">
-        <v>35</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>102</v>
@@ -2651,7 +2621,7 @@
         <v>104</v>
       </c>
       <c r="J17" s="3">
-        <v>12</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18">
@@ -2659,39 +2629,39 @@
         <v>105</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="J18" s="3">
-        <v>54</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>48</v>
+        <v>111</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>50</v>
@@ -2700,97 +2670,95 @@
         <v>50</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="J19" s="3">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>112</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="J20" s="3">
-        <v>8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>119</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J21" s="3">
-        <v>60</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>50</v>
@@ -2799,172 +2767,170 @@
         <v>43</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>125</v>
+        <v>53</v>
       </c>
       <c r="J22" s="3">
-        <v>32</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F23" s="3"/>
+      <c r="F23" s="3" t="s">
+        <v>134</v>
+      </c>
       <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>131</v>
+        <v>66</v>
       </c>
       <c r="J23" s="3">
-        <v>13</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>134</v>
+        <v>50</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="J24" s="3">
-        <v>70</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="E25" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="J25" s="3">
         <v>43</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="J25" s="3">
-        <v>50</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="D26" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>144</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J26" s="3">
-        <v>43</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>147</v>
+        <v>48</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J27" s="3">
         <v>6</v>
@@ -2972,43 +2938,43 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>152</v>
+        <v>48</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>156</v>
+        <v>53</v>
       </c>
       <c r="J28" s="3">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="C29" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>50</v>
@@ -3021,30 +2987,30 @@
         <v>22</v>
       </c>
       <c r="H29" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="J29" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="E30" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
@@ -3057,24 +3023,24 @@
         <v>164</v>
       </c>
       <c r="J30" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
@@ -3084,111 +3050,111 @@
         <v>166</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="J31" s="3">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>152</v>
+        <v>48</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>169</v>
+        <v>50</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="J32" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="J33" s="3">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>160</v>
+        <v>41</v>
       </c>
       <c r="J34" s="3">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>177</v>
+        <v>141</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>50</v>
@@ -3201,10 +3167,10 @@
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="J35" s="3">
         <v>2</v>
@@ -3212,29 +3178,29 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>152</v>
+        <v>48</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>171</v>
+        <v>47</v>
       </c>
       <c r="J36" s="3">
         <v>1</v>
@@ -3242,13 +3208,13 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>50</v>
@@ -3261,57 +3227,57 @@
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>47</v>
+        <v>182</v>
       </c>
       <c r="J37" s="3">
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>132</v>
+        <v>183</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="J38" s="3">
-        <v>65</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>129</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>38</v>
@@ -3321,24 +3287,24 @@
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="J39" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>191</v>
+        <v>48</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>193</v>
+        <v>143</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>50</v>
@@ -3351,10 +3317,10 @@
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J40" s="3">
         <v>6</v>
@@ -3362,32 +3328,32 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>196</v>
+        <v>143</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>197</v>
+        <v>50</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="J41" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3395,10 +3361,10 @@
         <v>48</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>50</v>
@@ -3411,10 +3377,10 @@
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="J42" s="3">
         <v>5</v>
@@ -3425,13 +3391,13 @@
         <v>48</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>43</v>
@@ -3441,13 +3407,13 @@
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="J43" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -3455,10 +3421,10 @@
         <v>48</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>154</v>
+        <v>203</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>50</v>
@@ -3471,54 +3437,54 @@
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="J44" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>50</v>
+        <v>188</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>207</v>
+        <v>159</v>
       </c>
       <c r="J45" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>211</v>
+        <v>141</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>50</v>
@@ -3531,27 +3497,27 @@
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="J46" s="3">
-        <v>19</v>
+        <v>58</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>38</v>
@@ -3561,87 +3527,87 @@
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="J47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>152</v>
+        <v>48</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>154</v>
+        <v>214</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>219</v>
+        <v>173</v>
       </c>
       <c r="J48" s="3">
-        <v>57</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>152</v>
+        <v>216</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>189</v>
+        <v>143</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>151</v>
+        <v>61</v>
       </c>
       <c r="J49" s="3">
-        <v>6</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>152</v>
+        <v>219</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>223</v>
+        <v>155</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>224</v>
+        <v>50</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>38</v>
@@ -3651,24 +3617,24 @@
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>47</v>
+        <v>153</v>
       </c>
       <c r="J50" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>48</v>
+        <v>222</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>50</v>
@@ -3681,54 +3647,54 @@
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="J51" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>229</v>
+        <v>141</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>154</v>
+        <v>226</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>61</v>
+        <v>228</v>
       </c>
       <c r="J52" s="3">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>50</v>
@@ -3741,27 +3707,27 @@
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="J53" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>149</v>
+        <v>226</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>38</v>
@@ -3771,10 +3737,10 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="J54" s="3">
         <v>2</v>
@@ -3782,46 +3748,46 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>50</v>
+        <v>188</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>164</v>
+        <v>237</v>
       </c>
       <c r="J55" s="3">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>241</v>
+        <v>155</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>38</v>
@@ -3831,27 +3797,27 @@
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>243</v>
+        <v>164</v>
       </c>
       <c r="J56" s="3">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>244</v>
+        <v>141</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>38</v>
@@ -3861,10 +3827,10 @@
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="J57" s="3">
         <v>2</v>
@@ -3872,16 +3838,16 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>241</v>
+        <v>155</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>38</v>
@@ -3891,57 +3857,57 @@
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="J58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>249</v>
+        <v>42</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>196</v>
+        <v>245</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>197</v>
+        <v>123</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>252</v>
+        <v>164</v>
       </c>
       <c r="J59" s="3">
-        <v>63</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>152</v>
+        <v>247</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>149</v>
+        <v>184</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>38</v>
@@ -3951,10 +3917,10 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>171</v>
+        <v>47</v>
       </c>
       <c r="J60" s="3">
         <v>1</v>
@@ -3962,43 +3928,43 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>152</v>
+        <v>250</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="J61" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>152</v>
+        <v>253</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>50</v>
@@ -4011,27 +3977,27 @@
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="J62" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>42</v>
+        <v>256</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>259</v>
+        <v>147</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>260</v>
+        <v>143</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>43</v>
@@ -4041,24 +4007,24 @@
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="J63" s="3">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>50</v>
@@ -4071,24 +4037,24 @@
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>53</v>
+        <v>261</v>
       </c>
       <c r="J64" s="3">
-        <v>70</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>50</v>
@@ -4101,87 +4067,87 @@
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="J65" s="3">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>78</v>
+        <v>264</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>267</v>
+        <v>208</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>269</v>
+        <v>70</v>
       </c>
       <c r="J66" s="3">
-        <v>22</v>
+        <v>62</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>158</v>
+        <v>267</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>154</v>
+        <v>206</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>50</v>
+        <v>188</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="J67" s="3">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>38</v>
@@ -4191,116 +4157,116 @@
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J68" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>276</v>
+        <v>154</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>277</v>
+        <v>155</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>197</v>
+        <v>50</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>164</v>
+        <v>70</v>
       </c>
       <c r="J69" s="3">
-        <v>5</v>
+        <v>62</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>279</v>
+        <v>141</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>280</v>
+        <v>251</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F70" s="3" t="s">
-        <v>281</v>
-      </c>
+      <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="J70" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F71" s="3"/>
+      <c r="F71" s="3" t="s">
+        <v>277</v>
+      </c>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>180</v>
+        <v>66</v>
       </c>
       <c r="J71" s="3">
-        <v>2</v>
+        <v>51</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>148</v>
+        <v>280</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>50</v>
@@ -4313,27 +4279,27 @@
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>73</v>
+        <v>153</v>
       </c>
       <c r="J72" s="3">
-        <v>61</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>290</v>
+        <v>203</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>43</v>
@@ -4343,27 +4309,27 @@
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>292</v>
+        <v>47</v>
       </c>
       <c r="J73" s="3">
-        <v>69</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>152</v>
+        <v>285</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>189</v>
+        <v>287</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>38</v>
@@ -4373,10 +4339,10 @@
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>171</v>
+        <v>47</v>
       </c>
       <c r="J74" s="3">
         <v>1</v>
@@ -4384,45 +4350,43 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>296</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="J75" s="3">
-        <v>50</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>263</v>
+        <v>147</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>50</v>
@@ -4435,24 +4399,24 @@
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>164</v>
+        <v>294</v>
       </c>
       <c r="J76" s="3">
-        <v>5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>301</v>
+        <v>193</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>209</v>
+        <v>143</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>50</v>
@@ -4465,84 +4429,84 @@
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>47</v>
+        <v>297</v>
       </c>
       <c r="J77" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>304</v>
+        <v>147</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>305</v>
+        <v>143</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>47</v>
+        <v>300</v>
       </c>
       <c r="J78" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>154</v>
+        <v>203</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>174</v>
+        <v>304</v>
       </c>
       <c r="J79" s="3">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>310</v>
+        <v>120</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>158</v>
+        <v>305</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>50</v>
@@ -4555,70 +4519,72 @@
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>312</v>
+        <v>41</v>
       </c>
       <c r="J80" s="3">
-        <v>47</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>154</v>
+        <v>309</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>316</v>
+        <v>47</v>
       </c>
       <c r="J81" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>149</v>
+        <v>313</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F82" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>314</v>
+      </c>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>47</v>
+        <v>159</v>
       </c>
       <c r="J82" s="3">
         <v>0</v>
@@ -4626,59 +4592,59 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>209</v>
+        <v>143</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>323</v>
+        <v>153</v>
       </c>
       <c r="J83" s="3">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>325</v>
+        <v>248</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>326</v>
+        <v>184</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>47</v>
+        <v>159</v>
       </c>
       <c r="J84" s="3">
         <v>0</v>
@@ -4686,16 +4652,16 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>148</v>
+        <v>322</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>241</v>
+        <v>323</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>43</v>
@@ -4705,27 +4671,27 @@
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>330</v>
+        <v>159</v>
       </c>
       <c r="J85" s="3">
-        <v>67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>332</v>
+        <v>184</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>197</v>
+        <v>123</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>38</v>
@@ -4735,54 +4701,54 @@
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>164</v>
       </c>
       <c r="J86" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>335</v>
+        <v>208</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>164</v>
+        <v>61</v>
       </c>
       <c r="J87" s="3">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>280</v>
+        <v>154</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>50</v>
@@ -4795,119 +4761,117 @@
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>171</v>
+        <v>332</v>
       </c>
       <c r="J88" s="3">
-        <v>1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>276</v>
+        <v>334</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>340</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="J89" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>344</v>
+        <v>155</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>207</v>
+        <v>159</v>
       </c>
       <c r="J90" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="J91" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>217</v>
+        <v>343</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>38</v>
@@ -4917,27 +4881,27 @@
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="J92" s="3">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>352</v>
+        <v>326</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>149</v>
+        <v>184</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>38</v>
@@ -4947,137 +4911,47 @@
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="J93" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>149</v>
+        <v>349</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>171</v>
+        <v>228</v>
       </c>
       <c r="J94" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F95" s="3"/>
-      <c r="G95" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="I95" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J95" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="J96" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="I97" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="J97" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J97"/>
+  <autoFilter ref="A1:J94"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5172,9 +5046,6 @@
     <hyperlink ref="H92" r:id="rId91"/>
     <hyperlink ref="H93" r:id="rId92"/>
     <hyperlink ref="H94" r:id="rId93"/>
-    <hyperlink ref="H95" r:id="rId94"/>
-    <hyperlink ref="H96" r:id="rId95"/>
-    <hyperlink ref="H97" r:id="rId96"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5182,9 +5053,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="51" customWidth="1"/>
-    <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="1" max="1" width="49" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5216,32 +5087,32 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>35</v>
+        <v>157</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>36</v>
+        <v>143</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>46</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>48</v>
+        <v>192</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5249,18 +5120,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5268,18 +5139,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>300</v>
+        <v>141</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>301</v>
+        <v>211</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5287,18 +5158,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>302</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>303</v>
+        <v>141</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>304</v>
+        <v>242</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>305</v>
+        <v>155</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5306,18 +5177,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>306</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>149</v>
+        <v>313</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5325,18 +5196,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>325</v>
+        <v>248</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>326</v>
+        <v>184</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5344,18 +5215,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>357</v>
+        <v>321</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>358</v>
+        <v>322</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>189</v>
+        <v>323</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5363,11 +5234,49 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>359</v>
+        <v>324</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>338</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G11"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5377,6 +5286,8 @@
     <hyperlink ref="G7" r:id="rId6"/>
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
+    <hyperlink ref="G10" r:id="rId9"/>
+    <hyperlink ref="G11" r:id="rId10"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5390,55 +5301,55 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="B2" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="B4" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="B5" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>370</v>
+        <v>314</v>
       </c>
       <c r="B6" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="B7" s="3">
         <v>10</v>
@@ -5446,63 +5357,63 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>119</v>
+        <v>357</v>
       </c>
       <c r="B8" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>372</v>
+        <v>113</v>
       </c>
       <c r="B9" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="B10" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>281</v>
+        <v>359</v>
       </c>
       <c r="B11" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -5510,7 +5421,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5532,36 +5443,36 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>63</v>
+        <v>147</v>
       </c>
       <c r="B2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>158</v>
+        <v>76</v>
       </c>
       <c r="B3" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5569,7 +5480,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5577,7 +5488,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5585,7 +5496,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5601,7 +5512,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5609,7 +5520,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5617,7 +5528,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5625,7 +5536,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5633,7 +5544,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>276</v>
+        <v>251</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5641,7 +5552,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>347</v>
+        <v>326</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5663,23 +5574,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2">
@@ -5687,7 +5598,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C2" s="3">
         <v>19.0</v>
@@ -5701,13 +5612,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="C3" s="3">
-        <v>18.6</v>
+        <v>9.2</v>
       </c>
       <c r="D3" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -5715,10 +5626,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="C4" s="3">
-        <v>9.2</v>
+        <v>7.6</v>
       </c>
       <c r="D4" s="3">
         <v>3</v>
@@ -5729,13 +5640,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>35</v>
+        <v>147</v>
       </c>
       <c r="C5" s="3">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="D5" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -5743,13 +5654,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C6" s="3">
-        <v>6.0</v>
+        <v>7.1</v>
       </c>
       <c r="D6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -5757,13 +5668,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="C7" s="3">
         <v>6.0</v>
       </c>
       <c r="D7" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -5771,13 +5682,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>280</v>
+        <v>112</v>
       </c>
       <c r="C8" s="3">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="D8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -5785,10 +5696,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C9" s="3">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="D9" s="3">
         <v>3</v>
@@ -5799,13 +5710,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="C10" s="3">
         <v>3.6</v>
       </c>
       <c r="D10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -5813,13 +5724,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>276</v>
+        <v>57</v>
       </c>
       <c r="C11" s="3">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -5827,13 +5738,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>57</v>
+        <v>248</v>
       </c>
       <c r="C12" s="3">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -5841,13 +5752,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>133</v>
+        <v>251</v>
       </c>
       <c r="C13" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -5855,13 +5766,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>167</v>
+        <v>127</v>
       </c>
       <c r="C14" s="3">
         <v>2.4</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -5869,7 +5780,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>217</v>
+        <v>160</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5883,7 +5794,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>263</v>
+        <v>193</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5909,21 +5820,21 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3">
@@ -5931,10 +5842,10 @@
         <v>38</v>
       </c>
       <c r="B3" s="3">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4">
@@ -5942,10 +5853,10 @@
         <v>43</v>
       </c>
       <c r="B4" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -5964,7 +5875,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
     </row>
     <row r="2">
@@ -5972,12 +5883,12 @@
         <v>50</v>
       </c>
       <c r="B2" s="3">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B3" s="3">
         <v>19</v>
@@ -5988,12 +5899,12 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -6001,7 +5912,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -6009,7 +5920,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -6017,17 +5928,9 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -6052,10 +5955,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6067,10 +5970,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6087,7 +5990,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>57</v>
@@ -6096,22 +5999,22 @@
         <v>58</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>316</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3">
@@ -6119,31 +6022,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -6151,31 +6054,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
     </row>
     <row r="5">
@@ -6183,31 +6086,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>408</v>
+        <v>394</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
@@ -6215,31 +6118,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="F6" s="3">
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -6247,31 +6150,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="F7" s="3">
         <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>420</v>
+        <v>406</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8">
@@ -6279,31 +6182,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>349</v>
+        <v>408</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>217</v>
+        <v>409</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>154</v>
+        <v>410</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="F8" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>350</v>
+        <v>412</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -6311,31 +6214,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>215</v>
+        <v>415</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="F9" s="3">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10">
@@ -6343,31 +6246,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>431</v>
+        <v>161</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>432</v>
+        <v>384</v>
       </c>
       <c r="F10" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>435</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11">
@@ -6375,31 +6278,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>437</v>
+        <v>154</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>168</v>
+        <v>426</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="F11" s="3">
         <v>84</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>316</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12">
@@ -6407,31 +6310,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>148</v>
+        <v>430</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>441</v>
+        <v>203</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F12" s="3">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>423</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -6439,31 +6342,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>209</v>
+        <v>143</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="F13" s="3">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>104</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14">
@@ -6471,31 +6374,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>154</v>
+        <v>439</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="F14" s="3">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -6503,31 +6406,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="F15" s="3">
         <v>74</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>423</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16">
@@ -6535,31 +6438,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>277</v>
+        <v>206</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="F16" s="3">
         <v>70</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17">
@@ -6567,31 +6470,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="F17" s="3">
         <v>70</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18">
@@ -6599,31 +6502,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="F18" s="3">
         <v>68</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
     </row>
     <row r="19">
@@ -6631,28 +6534,28 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="F19" s="3">
         <v>61</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>66</v>
@@ -6663,31 +6566,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="F20" s="3">
         <v>57</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21">
@@ -6695,31 +6598,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="F21" s="3">
         <v>46</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W43.xlsx
+++ b/reports/devops-jobs-israel-2026-W43.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="480">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-21T11:38:03</t>
+    <t xml:space="preserve">2026-10-22T11:38:27</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -93,1384 +93,1363 @@
     <t xml:space="preserve">greenhouse</t>
   </si>
   <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bucket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seniority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Seen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Group Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Security, Argo CD, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4988909101?gh_jid=4988909101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4988910101?gh_jid=4988910101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineering Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/5010669101?gh_jid=5010669101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Helm, Pulumi, CloudFormation, Networking, Security, Argo CD, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8356511002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jfrog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Helm, Prometheus, Istio, MongoDB, Kafka, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7510102&amp;gh_jid=7510102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Experience (DevEx) Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Python, Security, Observability, Backstage/IDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4693375006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevSecOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4704221006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Director of Platform Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer, Traffic Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Istio, Service Mesh, Nginx, Networking, Observability, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8200807?gh_jid=8200807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/8264120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior IT Infrastructure Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8882905002?gh_jid=8882905002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yotpo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Engineer - Office of the CTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8211515?gh_jid=8211515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8873995002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orcasecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer- Edge Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saltsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, Docker, CI/CD, Helm, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://salt.security/job-board?gh_jid=5208152007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mantis Tech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-mantis-tech-4480023899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-priority-software-4477000056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deloitte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-deloitte-4479294849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4481194632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fullpath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fullpath-4480776925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4480982357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Backend Infrastructure Team (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-infrastructure-team-cortex-at-palo-alto-networks-4470803159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4469727405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4480881694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, AIOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-aiops-at-nvidia-4471970512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At-Bay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-at-bay-4471503422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4478219818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blockaid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-blockaid-4480236011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer - Core Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeen.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-core-platform-at-jeen-ai-4482092082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-comblack-4480971929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced DevOps Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-devops-engineer-cortex-at-palo-alto-networks-4462513797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4480488912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-check-point-software-4479304749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cellebrite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4479674975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4479116905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4480795007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4478985380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pontera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pontera-4481315450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4480868969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Webiks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-reliability-engineer-at-webiks-4482425775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AllCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4470273860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer לארגון פיננסי מוביל במרכז הארץ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%D7%9C%D7%90%D7%A8%D7%92%D7%95%D7%9F-%D7%A4%D7%99%D7%A0%D7%A0%D7%A1%D7%99-%D7%9E%D7%95%D7%91%D7%99%D7%9C-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%90%D7%A8%D7%A5-at-jobist-4477738635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4482082697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integress, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-integress-inc-4479934720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4478251445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4478276676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-controp-precision-technologies-ltd-4479972286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application DevOps Engineer (1006977)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-devops-engineer-1006977-at-elad-software-systems-4481553636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Technical Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pacaya HR Experts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-technical-lead-at-pacaya-hr-experts-4479930327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-site-reliability-engineer-at-palo-alto-networks-4470801230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4481187900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops / SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIQAI Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-sre-at-uniqai-systems-4478231249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-confidential-careers-4476662621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-infrastructure-engineer-at-akamai-technologies-4473769865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pacaya-hr-experts-4479924948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-immunai-4482405033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-jobgether-4480437632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps &amp; Cloud Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-cloud-infrastructure-at-nimble-4450219176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4481195604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-at-lendbuzz-4477980904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer - AI Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-ai-platforms-at-palo-alto-networks-4471749164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guesty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-guesty-4473205757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software developer and DevOps engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysBind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-developer-and-devops-engineer-at-sysbind-4478663562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Engineer (GCP Focus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MyOps by Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-gcp-focus-at-myops-by-yael-group-4478218206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-at-confidential-careers-4480017132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-at-moveo-source-4480775799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-e2e-solutions-il-4479421024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-logica-it-4479496280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Administrator (1007969)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-1007969-at-elad-software-systems-4482089049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4478983773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer (10296)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bynet Data Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-10296-at-bynet-data-communications-4478972863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Administrator - position no. 1768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBI Investment House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-position-no-1768-at-ibi-investment-house-4478254402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4482435047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=8264438&amp;gh_jid=8264438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux &amp; HPC Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novocure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirat HaCarmel, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-novocure-4478872342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New York City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7995568003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Integration Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annapurna Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-student-spiv-team-at-annapurna-labs-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform/IaC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elapsed (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">indeed_il</t>
+  </si>
+  <si>
     <t xml:space="preserve">lever</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bucket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seniority</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Seen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Group Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Security, Argo CD, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4988909101?gh_jid=4988909101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4988910101?gh_jid=4988910101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineering Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/5010669101?gh_jid=5010669101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Helm, Pulumi, CloudFormation, Networking, Security, Argo CD, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8356511002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jfrog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Helm, Prometheus, Istio, MongoDB, Kafka, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7510102&amp;gh_jid=7510102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Experience (DevEx) Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Python, Security, Observability, Backstage/IDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4693375006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevSecOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4704221006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Director of Platform Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer, Traffic Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Istio, Service Mesh, Nginx, Networking, Observability, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8200807?gh_jid=8200807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Developer – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Docker, Linux, Prometheus, Grafana, MySQL, Redis, Kafka, Observability, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8176684?gh_jid=8176684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/8264120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior IT Infrastructure Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8882905002?gh_jid=8882905002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yotpo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Engineer - Office of the CTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8211515?gh_jid=8211515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8873995002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orcasecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer- Edge Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saltsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Docker, CI/CD, Helm, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://salt.security/job-board?gh_jid=5208152007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer (Prisma Browser)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-prisma-browser-at-palo-alto-networks-4469323268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-priority-software-4477000056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451477598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fullpath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fullpath-4480776925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4480982357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - Backend Infrastructure Team (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-infrastructure-team-cortex-at-palo-alto-networks-4470803159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4469727405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4480881694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">At-Bay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-at-bay-4471503422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4478219818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blockaid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-blockaid-4480236011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-comblack-4480971929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARAN Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aran-software-4479824052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4478465745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4480488912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-check-point-software-4479304749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cellebrite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4479674975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4479116905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4480795007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4478985380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4480868969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SeeTrue AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-devops-engineer-at-seetrue-ai-4477069152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps &amp; AI Enablement Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xsight Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-ai-enablement-engineer-at-xsight-labs-4471491552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AllCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4470273860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer לארגון פיננסי מוביל במרכז הארץ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%D7%9C%D7%90%D7%A8%D7%92%D7%95%D7%9F-%D7%A4%D7%99%D7%A0%D7%A0%D7%A1%D7%99-%D7%9E%D7%95%D7%91%D7%99%D7%9C-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%90%D7%A8%D7%A5-at-jobist-4477738635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integress, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-integress-inc-4479934720</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4478251445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4478276676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4482049895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-controp-precision-technologies-ltd-4479972286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application DevOps Engineer (1006977)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-devops-engineer-1006977-at-elad-software-systems-4481553636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Technical Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pacaya HR Experts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-technical-lead-at-pacaya-hr-experts-4479930327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops / SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIQAI Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-sre-at-uniqai-systems-4478231249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE Engineer /Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-site-reliability-engineer-at-palo-alto-networks-4470801230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-confidential-careers-4476662621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4478209649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pacaya-hr-experts-4479924948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Engineer (Infra Platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-infra-platform-at-monday-com-4479587116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Full Stack Engineer – DevOps &amp; Cloud Focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sheba Medical Center, Tel Hashomer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-full-stack-engineer-%E2%80%93-devops-cloud-focus-at-sheba-medical-center-tel-hashomer-4478671787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-jobgether-4480437632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps &amp; Cloud Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-cloud-infrastructure-at-nimble-4450219176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-at-lendbuzz-4477980904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer - AI Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-ai-platforms-at-palo-alto-networks-4471749164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guesty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-guesty-4473205757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software developer and DevOps engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysBind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-developer-and-devops-engineer-at-sysbind-4478663562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Engineer (GCP Focus)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MyOps by Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-gcp-focus-at-myops-by-yael-group-4478218206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infra Engineer Team Lead - IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScaleOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-team-lead-il-at-scaleops-4479538658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Infrastructure Engineer (1007969)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-1007969-at-elad-software-systems-4482089049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-at-moveo-source-4480775799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (37823)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-37823-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4480979267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer, NCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-4453269633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4478983773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer (10296)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bynet Data Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-10296-at-bynet-data-communications-4478972863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Administrator - position no. 1768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBI Investment House</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-position-no-1768-at-ibi-investment-house-4478254402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INGIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4481565145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (37562)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-37562-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4480965834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mendix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boston, MA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://jobs.lever.co/mendix/f61ca692-a66b-4e9f-a864-ad29e7cd716e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=8264438&amp;gh_jid=8264438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux &amp; HPC Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novocure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tirat HaCarmel, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-novocure-4478872342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New York City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7995568003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Integration Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-student-spiv-team-at-amazon-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elapsed (s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">indeed_il</t>
   </si>
   <si>
     <t xml:space="preserve">alljobs</t>
@@ -1612,7 +1591,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -1628,7 +1607,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>846</v>
+        <v>852</v>
       </c>
     </row>
     <row r="10">
@@ -1700,7 +1679,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20">
@@ -1708,15 +1687,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="3">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1732,31 +1703,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B3" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B4" s="3">
         <v>8</v>
@@ -1764,7 +1735,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -1772,7 +1743,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -1780,7 +1751,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1799,23 +1770,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="B2" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B3" s="3">
         <v>28</v>
@@ -1823,39 +1794,39 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>475</v>
+        <v>359</v>
       </c>
       <c r="B4" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>360</v>
+        <v>467</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B6" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B7" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="B8" s="3">
         <v>20</v>
@@ -1863,7 +1834,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="B9" s="3">
         <v>19</v>
@@ -1871,23 +1842,23 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B12" s="3">
         <v>12</v>
@@ -1895,15 +1866,15 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B13" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B14" s="3">
         <v>10</v>
@@ -1911,18 +1882,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B16" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1947,13 +1918,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
     </row>
     <row r="2">
@@ -1961,13 +1932,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3">
-        <v>11.3</v>
+        <v>12.2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1976,88 +1947,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3">
-        <v>38.5</v>
+        <v>34.3</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.5</v>
+        <v>8.7</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>24</v>
+        <v>476</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>28.8</v>
+        <v>33.9</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>14.9</v>
+        <v>16.3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>19.4</v>
+        <v>37.3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2082,595 +2053,595 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J2" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="F3" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J3" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="J4" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="C5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="J5" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J6" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="J7" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="J8" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="J9" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="J10" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="I11" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="J11" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="J12" s="3">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="J13" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="C14" s="3" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J14" s="3">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H15" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="J15" s="3">
-        <v>13</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J16" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J17" s="3">
-        <v>65</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J18" s="3">
-        <v>9</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>113</v>
@@ -2685,7 +2656,7 @@
         <v>115</v>
       </c>
       <c r="J19" s="3">
-        <v>61</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
@@ -2693,110 +2664,110 @@
         <v>116</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>117</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J20" s="3">
-        <v>33</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F21" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>125</v>
+      </c>
       <c r="G21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>125</v>
+        <v>52</v>
       </c>
       <c r="J21" s="3">
-        <v>14</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="J22" s="3">
-        <v>71</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>134</v>
@@ -2808,33 +2779,31 @@
         <v>135</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="J23" s="3">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>137</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>138</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>139</v>
@@ -2843,247 +2812,247 @@
         <v>140</v>
       </c>
       <c r="J24" s="3">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="C25" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J25" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J26" s="3">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J27" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="J28" s="3">
-        <v>71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J29" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>162</v>
-      </c>
       <c r="E30" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J30" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H31" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="I31" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="J31" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H32" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="J32" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33">
@@ -3094,13 +3063,13 @@
         <v>171</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
@@ -3113,24 +3082,24 @@
         <v>173</v>
       </c>
       <c r="J33" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
@@ -3140,147 +3109,147 @@
         <v>175</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>41</v>
+        <v>176</v>
       </c>
       <c r="J34" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>164</v>
+        <v>40</v>
       </c>
       <c r="J35" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>47</v>
+        <v>162</v>
       </c>
       <c r="J36" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
       <c r="J37" s="3">
-        <v>66</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="C38" s="3" t="s">
-        <v>184</v>
+        <v>138</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="I38" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="J38" s="3">
-        <v>2</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>141</v>
+        <v>186</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>188</v>
+        <v>119</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
@@ -3290,27 +3259,27 @@
         <v>189</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="J39" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>48</v>
+        <v>190</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>143</v>
+        <v>188</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
@@ -3320,10 +3289,10 @@
         <v>191</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="J40" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -3331,26 +3300,26 @@
         <v>192</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="J41" s="3">
         <v>0</v>
@@ -3358,19 +3327,19 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>48</v>
+        <v>194</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>195</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
@@ -3380,147 +3349,147 @@
         <v>196</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>197</v>
+        <v>157</v>
       </c>
       <c r="J42" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>199</v>
+        <v>138</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>200</v>
+        <v>49</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="J43" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="E44" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="J44" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>141</v>
+        <v>47</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="D45" s="3" t="s">
-        <v>188</v>
+        <v>49</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>159</v>
+        <v>199</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="D46" s="3" t="s">
-        <v>50</v>
+        <v>209</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>210</v>
+        <v>157</v>
       </c>
       <c r="J46" s="3">
-        <v>58</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>211</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>184</v>
+        <v>138</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
@@ -3530,27 +3499,27 @@
         <v>212</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>159</v>
+        <v>213</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
@@ -3560,27 +3529,27 @@
         <v>215</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="J48" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="D49" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
@@ -3590,27 +3559,27 @@
         <v>218</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="J49" s="3">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="D50" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
@@ -3620,10 +3589,10 @@
         <v>221</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="J50" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -3634,13 +3603,13 @@
         <v>223</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>214</v>
+        <v>138</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
@@ -3650,27 +3619,27 @@
         <v>224</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>153</v>
+        <v>60</v>
       </c>
       <c r="J51" s="3">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>141</v>
+        <v>225</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>226</v>
+        <v>149</v>
       </c>
       <c r="D52" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E52" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
@@ -3680,57 +3649,57 @@
         <v>227</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>228</v>
+        <v>140</v>
       </c>
       <c r="J52" s="3">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>229</v>
+        <v>94</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>173</v>
+        <v>230</v>
       </c>
       <c r="J53" s="3">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>141</v>
+        <v>231</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>232</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>226</v>
+        <v>138</v>
       </c>
       <c r="D54" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
@@ -3740,10 +3709,10 @@
         <v>233</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="J54" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -3751,76 +3720,76 @@
         <v>234</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>235</v>
+        <v>187</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>188</v>
+        <v>119</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>237</v>
+        <v>140</v>
       </c>
       <c r="J55" s="3">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J56" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>141</v>
+        <v>238</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="D57" s="3" t="s">
-        <v>123</v>
+        <v>209</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
@@ -3830,57 +3799,57 @@
         <v>241</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>164</v>
+        <v>242</v>
       </c>
       <c r="J57" s="3">
-        <v>2</v>
+        <v>65</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>245</v>
+        <v>188</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
@@ -3890,27 +3859,27 @@
         <v>246</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J59" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="C60" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="D60" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
@@ -3920,10 +3889,10 @@
         <v>249</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>47</v>
+        <v>162</v>
       </c>
       <c r="J60" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -3934,13 +3903,13 @@
         <v>251</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
@@ -3950,7 +3919,7 @@
         <v>252</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>164</v>
+        <v>46</v>
       </c>
       <c r="J61" s="3">
         <v>2</v>
@@ -3964,13 +3933,13 @@
         <v>254</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>203</v>
+        <v>149</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
@@ -3980,10 +3949,10 @@
         <v>255</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J62" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -3991,16 +3960,16 @@
         <v>256</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
@@ -4010,10 +3979,10 @@
         <v>257</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J63" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64">
@@ -4021,89 +3990,89 @@
         <v>258</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>259</v>
+        <v>164</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>261</v>
+        <v>166</v>
       </c>
       <c r="J64" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>147</v>
+        <v>211</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="J65" s="3">
-        <v>24</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>208</v>
+        <v>263</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="I66" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="J66" s="3">
-        <v>62</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67">
@@ -4111,16 +4080,16 @@
         <v>266</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="D67" s="3" t="s">
-        <v>188</v>
+        <v>119</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
@@ -4130,10 +4099,10 @@
         <v>268</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="J67" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4144,13 +4113,13 @@
         <v>270</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
@@ -4160,7 +4129,7 @@
         <v>271</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="J68" s="3">
         <v>3</v>
@@ -4171,80 +4140,78 @@
         <v>272</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>154</v>
+        <v>273</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>155</v>
+        <v>208</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>50</v>
+        <v>209</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>70</v>
+        <v>147</v>
       </c>
       <c r="J69" s="3">
-        <v>62</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>141</v>
+        <v>275</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>184</v>
+        <v>138</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="J70" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>275</v>
+        <v>94</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>277</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
@@ -4252,10 +4219,10 @@
         <v>278</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>66</v>
+        <v>162</v>
       </c>
       <c r="J71" s="3">
-        <v>51</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -4266,13 +4233,13 @@
         <v>280</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
@@ -4282,10 +4249,10 @@
         <v>281</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="J72" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4296,146 +4263,148 @@
         <v>283</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>203</v>
+        <v>149</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F73" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>284</v>
+      </c>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="J73" s="3">
-        <v>1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J74" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J75" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J76" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>193</v>
+        <v>152</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>143</v>
+        <v>267</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>297</v>
+        <v>140</v>
       </c>
       <c r="J77" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4443,16 +4412,16 @@
         <v>298</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
@@ -4465,7 +4434,7 @@
         <v>300</v>
       </c>
       <c r="J78" s="3">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79">
@@ -4473,46 +4442,46 @@
         <v>301</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>302</v>
+        <v>164</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>203</v>
+        <v>138</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="I79" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="I79" s="3" t="s">
-        <v>304</v>
-      </c>
       <c r="J79" s="3">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>120</v>
+        <v>304</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>305</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
@@ -4522,159 +4491,159 @@
         <v>306</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>41</v>
+        <v>265</v>
       </c>
       <c r="J80" s="3">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>308</v>
-      </c>
       <c r="C81" s="3" t="s">
-        <v>309</v>
+        <v>138</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J81" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="D82" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H82" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C82" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>315</v>
-      </c>
       <c r="I82" s="3" t="s">
-        <v>159</v>
+        <v>46</v>
       </c>
       <c r="J82" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F83" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="G83" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H83" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="C83" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F83" s="3"/>
-      <c r="G83" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>318</v>
-      </c>
       <c r="I83" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="J83" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>248</v>
+        <v>152</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>159</v>
+        <v>69</v>
       </c>
       <c r="J84" s="3">
-        <v>0</v>
+        <v>63</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>322</v>
+        <v>273</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>323</v>
+        <v>188</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="J85" s="3">
         <v>0</v>
@@ -4682,49 +4651,49 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>184</v>
+        <v>324</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="J86" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="B87" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="D87" s="3" t="s">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
@@ -4734,10 +4703,10 @@
         <v>329</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="J87" s="3">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -4745,29 +4714,29 @@
         <v>330</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>154</v>
+        <v>331</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>332</v>
+        <v>140</v>
       </c>
       <c r="J88" s="3">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -4775,116 +4744,116 @@
         <v>333</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>334</v>
+        <v>211</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>159</v>
+        <v>60</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>337</v>
+        <v>251</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J90" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="J91" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>47</v>
+        <v>157</v>
       </c>
       <c r="J92" s="3">
         <v>1</v>
@@ -4892,62 +4861,62 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J93" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="B94" s="3" t="s">
-        <v>348</v>
-      </c>
       <c r="C94" s="3" t="s">
-        <v>349</v>
+        <v>188</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>228</v>
+        <v>140</v>
       </c>
       <c r="J94" s="3">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5053,9 +5022,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="49" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5064,36 +5033,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5101,18 +5070,18 @@
         <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>193</v>
+        <v>152</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5120,18 +5089,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>194</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>141</v>
+        <v>186</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5139,18 +5108,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>141</v>
+        <v>192</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>211</v>
+        <v>164</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5158,18 +5127,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5177,18 +5146,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>311</v>
+        <v>225</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>312</v>
+        <v>226</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>313</v>
+        <v>149</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5196,18 +5165,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>315</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>319</v>
+        <v>234</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>248</v>
+        <v>187</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5215,18 +5184,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>320</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>321</v>
+        <v>266</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>322</v>
+        <v>152</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>323</v>
+        <v>267</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5234,18 +5203,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>324</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>333</v>
+        <v>279</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>334</v>
+        <v>280</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>155</v>
+        <v>205</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5253,18 +5222,18 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>335</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>336</v>
+        <v>296</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>337</v>
+        <v>152</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>155</v>
+        <v>267</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5272,11 +5241,87 @@
         <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>338</v>
+        <v>297</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>348</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G15"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5288,6 +5333,10 @@
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
     <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
+    <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5301,23 +5350,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B3" s="3">
         <v>16</v>
@@ -5325,7 +5374,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B4" s="3">
         <v>14</v>
@@ -5333,7 +5382,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B5" s="3">
         <v>14</v>
@@ -5341,7 +5390,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B6" s="3">
         <v>10</v>
@@ -5349,15 +5398,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B7" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B8" s="3">
         <v>9</v>
@@ -5365,7 +5414,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>113</v>
+        <v>356</v>
       </c>
       <c r="B9" s="3">
         <v>8</v>
@@ -5373,15 +5422,15 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>358</v>
+        <v>109</v>
       </c>
       <c r="B10" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B11" s="3">
         <v>7</v>
@@ -5389,7 +5438,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -5397,15 +5446,15 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -5413,7 +5462,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -5421,7 +5470,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5434,21 +5483,21 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="B2" s="3">
         <v>6</v>
@@ -5456,15 +5505,15 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="B3" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5472,7 +5521,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5480,7 +5529,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5488,7 +5537,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>154</v>
+        <v>89</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5496,7 +5545,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5504,7 +5553,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5512,7 +5561,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5520,7 +5569,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5528,7 +5577,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5536,7 +5585,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>248</v>
+        <v>195</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5552,7 +5601,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>326</v>
+        <v>254</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5560,10 +5609,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>57</v>
+        <v>273</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5581,16 +5630,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2">
@@ -5598,13 +5647,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" s="3">
-        <v>19.0</v>
+        <v>13.4</v>
       </c>
       <c r="D2" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -5612,7 +5661,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C3" s="3">
         <v>9.2</v>
@@ -5626,13 +5675,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>63</v>
+        <v>164</v>
       </c>
       <c r="C4" s="3">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="D4" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -5640,13 +5689,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>147</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="D5" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -5654,7 +5703,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" s="3">
         <v>7.1</v>
@@ -5668,7 +5717,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="3">
         <v>6.0</v>
@@ -5682,13 +5731,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>112</v>
+        <v>152</v>
       </c>
       <c r="C8" s="3">
-        <v>3.6</v>
+        <v>6.0</v>
       </c>
       <c r="D8" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -5696,13 +5745,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="C9" s="3">
         <v>3.6</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -5710,7 +5759,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C10" s="3">
         <v>3.6</v>
@@ -5724,7 +5773,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C11" s="3">
         <v>2.9</v>
@@ -5738,7 +5787,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C12" s="3">
         <v>2.8</v>
@@ -5752,7 +5801,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -5766,7 +5815,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C14" s="3">
         <v>2.4</v>
@@ -5780,7 +5829,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5794,7 +5843,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5817,46 +5866,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" s="3">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -5872,55 +5921,55 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -5928,7 +5977,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -5955,34 +6004,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>376</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -5990,31 +6039,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3">
@@ -6022,31 +6071,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>382</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>384</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>385</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -6054,31 +6103,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>388</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>390</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>391</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="5">
@@ -6086,31 +6135,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>394</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>396</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6">
@@ -6118,31 +6167,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F6" s="3">
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7">
@@ -6150,31 +6199,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>405</v>
-      </c>
       <c r="E7" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F7" s="3">
         <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8">
@@ -6182,31 +6231,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>408</v>
+        <v>333</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>409</v>
+        <v>211</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>410</v>
+        <v>138</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F8" s="3">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>412</v>
+        <v>334</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>413</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9">
@@ -6214,31 +6263,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>416</v>
+        <v>328</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>417</v>
+        <v>382</v>
       </c>
       <c r="F9" s="3">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
     </row>
     <row r="10">
@@ -6246,31 +6295,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>161</v>
+        <v>414</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>384</v>
+        <v>415</v>
       </c>
       <c r="F10" s="3">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>297</v>
+        <v>418</v>
       </c>
     </row>
     <row r="11">
@@ -6278,28 +6327,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>154</v>
+        <v>420</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>426</v>
+        <v>159</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F11" s="3">
         <v>84</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>300</v>
@@ -6310,31 +6359,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>430</v>
+        <v>152</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>203</v>
+        <v>267</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="F12" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>98</v>
+        <v>303</v>
       </c>
     </row>
     <row r="13">
@@ -6342,31 +6391,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="F13" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>237</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -6374,31 +6423,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>439</v>
+        <v>138</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F14" s="3">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>47</v>
+        <v>242</v>
       </c>
     </row>
     <row r="15">
@@ -6406,31 +6455,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>203</v>
+        <v>436</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>396</v>
+        <v>376</v>
       </c>
       <c r="F15" s="3">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>300</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
@@ -6438,31 +6487,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F16" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>70</v>
+        <v>303</v>
       </c>
     </row>
     <row r="17">
@@ -6470,31 +6519,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>395</v>
+        <v>443</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F17" s="3">
         <v>70</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>125</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18">
@@ -6502,31 +6551,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>453</v>
+        <v>393</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>454</v>
+        <v>153</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="F18" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>457</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19">
@@ -6534,31 +6583,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>143</v>
+        <v>451</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F19" s="3">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>66</v>
+        <v>454</v>
       </c>
     </row>
     <row r="20">
@@ -6566,31 +6615,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>187</v>
+        <v>138</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>417</v>
+        <v>376</v>
       </c>
       <c r="F20" s="3">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21">
@@ -6598,31 +6647,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>184</v>
+        <v>240</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F21" s="3">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>470</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W43.xlsx
+++ b/reports/devops-jobs-israel-2026-W43.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="478">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-22T11:38:27</t>
+    <t xml:space="preserve">2026-10-23T11:27:54</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -432,70 +432,559 @@
     <t xml:space="preserve">2026-09-07</t>
   </si>
   <si>
-    <t xml:space="preserve">Mantis Tech</t>
+    <t xml:space="preserve">Aidoc</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-mantis-tech-4480023899</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4465646027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-priority-software-4477000056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deloitte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-deloitte-4479294849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4481638138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fullpath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fullpath-4480776925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Backend Infrastructure Team (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-infrastructure-team-cortex-at-palo-alto-networks-4470803159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4469727405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4480881694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, AIOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-aiops-at-nvidia-4471970512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer and SRE Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upstream Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-and-sre-lead-at-upstream-security-4482467626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At-Bay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-at-bay-4471503422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4478219818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blockaid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-blockaid-4480236011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer - Core Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeen.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-core-platform-at-jeen-ai-4482092082</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-22</t>
   </si>
   <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-priority-software-4477000056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deloitte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-deloitte-4479294849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
+    <t xml:space="preserve">DevOps Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-comblack-4480971929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4480488912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cellebrite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4479674975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4480795007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4478985380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pontera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pontera-4481315450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4480868969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4482494409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer | Build &amp; Lead Cloud Infrastructure at a Cutting-Edge Cybersecurity Startup 🚀</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pacaya HR Experts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-build-lead-cloud-infrastructure-at-a-cutting-edge-cybersecurity-startup-%F0%9F%9A%80-at-pacaya-hr-experts-4479930327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Webiks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-reliability-engineer-at-webiks-4482425775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AllCloud</t>
   </si>
   <si>
     <t xml:space="preserve">Raanana, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4481194632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fullpath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fullpath-4480776925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4470273860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4482082697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integress, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-integress-inc-4479934720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4478276676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-controp-precision-technologies-ltd-4479972286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application DevOps Engineer (1006977)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-devops-engineer-1006977-at-elad-software-systems-4481553636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops / SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIQAI Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-sre-at-uniqai-systems-4478231249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-at-lendbuzz-4477980904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antidote Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-antidote-health-4480773737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-site-reliability-engineer-at-palo-alto-networks-4470801230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-confidential-careers-4476662621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Integrator SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-integrator-sre-at-moveo-source-4481380188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-infrastructure-engineer-at-akamai-technologies-4473769865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-immunai-4482405033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-jobgether-4480437632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps &amp; Cloud Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-cloud-infrastructure-at-nimble-4450219176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guesty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-guesty-4473205757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software developer and DevOps engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysBind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-developer-and-devops-engineer-at-sysbind-4478663562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Engineer (GCP Focus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MyOps by Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-gcp-focus-at-myops-by-yael-group-4478218206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-at-confidential-careers-4480017132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-at-moveo-source-4480775799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-e2e-solutions-il-4479421024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
   </si>
   <si>
     <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
@@ -504,744 +993,231 @@
     <t xml:space="preserve">Jerusalem</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4480982357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - Backend Infrastructure Team (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-infrastructure-team-cortex-at-palo-alto-networks-4470803159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4469727405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4480881694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, AIOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-aiops-at-nvidia-4471970512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">At-Bay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-at-bay-4471503422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4478219818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blockaid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-blockaid-4480236011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform DevOps Engineer - Core Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeen.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-core-platform-at-jeen-ai-4482092082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-comblack-4480971929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced DevOps Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-devops-engineer-cortex-at-palo-alto-networks-4462513797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4480488912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-check-point-software-4479304749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cellebrite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4479674975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4479116905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4480795007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4478985380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pontera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pontera-4481315450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4480868969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Webiks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-reliability-engineer-at-webiks-4482425775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AllCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4470273860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer לארגון פיננסי מוביל במרכז הארץ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%D7%9C%D7%90%D7%A8%D7%92%D7%95%D7%9F-%D7%A4%D7%99%D7%A0%D7%A0%D7%A1%D7%99-%D7%9E%D7%95%D7%91%D7%99%D7%9C-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%90%D7%A8%D7%A5-at-jobist-4477738635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4482082697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integress, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-integress-inc-4479934720</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4478251445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4478276676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-controp-precision-technologies-ltd-4479972286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application DevOps Engineer (1006977)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-devops-engineer-1006977-at-elad-software-systems-4481553636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Technical Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pacaya HR Experts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-technical-lead-at-pacaya-hr-experts-4479930327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-site-reliability-engineer-at-palo-alto-networks-4470801230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4481187900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops / SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIQAI Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-sre-at-uniqai-systems-4478231249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-confidential-careers-4476662621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-infrastructure-engineer-at-akamai-technologies-4473769865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pacaya-hr-experts-4479924948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immunai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-immunai-4482405033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-jobgether-4480437632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps &amp; Cloud Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-cloud-infrastructure-at-nimble-4450219176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4481195604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-at-lendbuzz-4477980904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer - AI Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-ai-platforms-at-palo-alto-networks-4471749164</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-logica-it-4479496280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (37823)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-37823-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4482463663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Administrator (1007969)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-1007969-at-elad-software-systems-4482089049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4478983773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Administrator - Cloud, Microsoft &amp; Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Octally Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-cloud-microsoft-infrastructure-at-octally-integration-4480045453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer (10296)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bynet Data Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-10296-at-bynet-data-communications-4478972863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Administrator - position no. 1768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBI Investment House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-position-no-1768-at-ibi-investment-house-4478254402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4482435047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=8264438&amp;gh_jid=8264438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux &amp; HPC Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novocure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirat HaCarmel, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-novocure-4478872342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-30</t>
   </si>
   <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guesty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-guesty-4473205757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software developer and DevOps engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysBind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-developer-and-devops-engineer-at-sysbind-4478663562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Engineer (GCP Focus)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MyOps by Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-gcp-focus-at-myops-by-yael-group-4478218206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-at-confidential-careers-4480017132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-at-moveo-source-4480775799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-e2e-solutions-il-4479421024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-logica-it-4479496280</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Administrator (1007969)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-1007969-at-elad-software-systems-4482089049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4478983773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer (10296)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bynet Data Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-10296-at-bynet-data-communications-4478972863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Administrator - position no. 1768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBI Investment House</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-position-no-1768-at-ibi-investment-house-4478254402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INGIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4482435047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=8264438&amp;gh_jid=8264438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux &amp; HPC Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novocure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tirat HaCarmel, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-novocure-4478872342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux System Administrator</t>
   </si>
   <si>
@@ -1290,15 +1266,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
   </si>
   <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
   </si>
   <si>
@@ -1408,6 +1375,33 @@
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Operations Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-compie-technologies-4482446270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
   </si>
   <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
@@ -1583,7 +1577,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
@@ -1591,7 +1585,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1599,7 +1593,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
@@ -1607,7 +1601,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>852</v>
+        <v>859</v>
       </c>
     </row>
     <row r="10">
@@ -1679,7 +1673,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -1706,28 +1700,28 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="B3" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>394</v>
+        <v>373</v>
       </c>
       <c r="B4" s="3">
         <v>8</v>
@@ -1735,7 +1729,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -1743,18 +1737,10 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="B7" s="3">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1770,79 +1756,79 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B2" s="3">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B3" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>359</v>
+        <v>465</v>
       </c>
       <c r="B4" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>467</v>
+        <v>355</v>
       </c>
       <c r="B5" s="3">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B6" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B7" s="3">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B8" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B9" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>355</v>
+        <v>283</v>
       </c>
       <c r="B10" s="3">
         <v>13</v>
@@ -1850,50 +1836,50 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>284</v>
+        <v>352</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B13" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B14" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B15" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B16" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1918,13 +1904,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>471</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="2">
@@ -1935,10 +1921,10 @@
         <v>22</v>
       </c>
       <c r="C2" s="3">
-        <v>12.2</v>
+        <v>13.1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1947,88 +1933,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C3" s="3">
-        <v>34.3</v>
+        <v>36.7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.7</v>
+        <v>8.2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>33.9</v>
+        <v>30.3</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>16.3</v>
+        <v>15.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>37.3</v>
+        <v>32.6</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2112,7 +2098,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -2144,7 +2130,7 @@
         <v>40</v>
       </c>
       <c r="J3" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -2176,7 +2162,7 @@
         <v>46</v>
       </c>
       <c r="J4" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -2208,7 +2194,7 @@
         <v>52</v>
       </c>
       <c r="J5" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6">
@@ -2240,7 +2226,7 @@
         <v>52</v>
       </c>
       <c r="J6" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
@@ -2272,7 +2258,7 @@
         <v>60</v>
       </c>
       <c r="J7" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
@@ -2304,7 +2290,7 @@
         <v>65</v>
       </c>
       <c r="J8" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9">
@@ -2336,7 +2322,7 @@
         <v>69</v>
       </c>
       <c r="J9" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
@@ -2368,7 +2354,7 @@
         <v>73</v>
       </c>
       <c r="J10" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
@@ -2400,7 +2386,7 @@
         <v>79</v>
       </c>
       <c r="J11" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
@@ -2432,7 +2418,7 @@
         <v>83</v>
       </c>
       <c r="J12" s="3">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13">
@@ -2464,7 +2450,7 @@
         <v>87</v>
       </c>
       <c r="J13" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -2496,7 +2482,7 @@
         <v>93</v>
       </c>
       <c r="J14" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -2528,7 +2514,7 @@
         <v>97</v>
       </c>
       <c r="J15" s="3">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16">
@@ -2560,7 +2546,7 @@
         <v>73</v>
       </c>
       <c r="J16" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
@@ -2592,7 +2578,7 @@
         <v>106</v>
       </c>
       <c r="J17" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -2624,7 +2610,7 @@
         <v>111</v>
       </c>
       <c r="J18" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
@@ -2656,7 +2642,7 @@
         <v>115</v>
       </c>
       <c r="J19" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
@@ -2686,7 +2672,7 @@
         <v>121</v>
       </c>
       <c r="J20" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -2718,7 +2704,7 @@
         <v>52</v>
       </c>
       <c r="J21" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22">
@@ -2750,7 +2736,7 @@
         <v>65</v>
       </c>
       <c r="J22" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23">
@@ -2782,12 +2768,12 @@
         <v>136</v>
       </c>
       <c r="J23" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>137</v>
@@ -2799,7 +2785,7 @@
         <v>49</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
@@ -2809,10 +2795,10 @@
         <v>139</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="J24" s="3">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25">
@@ -2820,7 +2806,7 @@
         <v>94</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>138</v>
@@ -2836,13 +2822,13 @@
         <v>22</v>
       </c>
       <c r="H25" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="I25" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="J25" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26">
@@ -2850,10 +2836,10 @@
         <v>47</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>119</v>
@@ -2866,13 +2852,13 @@
         <v>22</v>
       </c>
       <c r="H26" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="J26" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -2880,10 +2866,10 @@
         <v>94</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>49</v>
@@ -2896,27 +2882,27 @@
         <v>22</v>
       </c>
       <c r="H27" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="J27" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>47</v>
+        <v>151</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>152</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>42</v>
@@ -2926,13 +2912,13 @@
         <v>22</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="J28" s="3">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29">
@@ -2940,13 +2926,13 @@
         <v>47</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="D29" s="3" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>42</v>
@@ -2962,45 +2948,45 @@
         <v>157</v>
       </c>
       <c r="J29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>158</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>160</v>
+        <v>49</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J30" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>138</v>
@@ -3016,13 +3002,13 @@
         <v>22</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="J31" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32">
@@ -3030,7 +3016,7 @@
         <v>47</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>138</v>
@@ -3046,21 +3032,21 @@
         <v>22</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="J32" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>138</v>
@@ -3076,24 +3062,24 @@
         <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J33" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>49</v>
@@ -3106,43 +3092,43 @@
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="J34" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>94</v>
+        <v>174</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>138</v>
+        <v>176</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>40</v>
+        <v>157</v>
       </c>
       <c r="J35" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3150,7 +3136,7 @@
         <v>94</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>138</v>
@@ -3166,21 +3152,21 @@
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>162</v>
+        <v>40</v>
       </c>
       <c r="J36" s="3">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>138</v>
@@ -3189,25 +3175,25 @@
         <v>49</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="I37" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="J37" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>183</v>
@@ -3229,51 +3215,51 @@
         <v>184</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>185</v>
+        <v>46</v>
       </c>
       <c r="J38" s="3">
-        <v>67</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>186</v>
+        <v>122</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>188</v>
+        <v>138</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="J39" s="3">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>188</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>119</v>
@@ -3289,24 +3275,24 @@
         <v>191</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="J40" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>149</v>
+        <v>190</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>37</v>
@@ -3316,21 +3302,21 @@
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="J41" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>138</v>
@@ -3346,13 +3332,13 @@
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J42" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -3360,13 +3346,13 @@
         <v>47</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>138</v>
+        <v>200</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>49</v>
+        <v>201</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>42</v>
@@ -3376,73 +3362,73 @@
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="J43" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="J44" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>205</v>
+        <v>138</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="J45" s="3">
-        <v>6</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46">
@@ -3450,13 +3436,13 @@
         <v>94</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>209</v>
+        <v>119</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>37</v>
@@ -3466,13 +3452,13 @@
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J46" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3480,10 +3466,10 @@
         <v>94</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>138</v>
+        <v>176</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>49</v>
@@ -3496,114 +3482,114 @@
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="J47" s="3">
-        <v>59</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>214</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="J48" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>94</v>
+        <v>217</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>217</v>
+        <v>138</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>49</v>
+        <v>205</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="J50" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="C51" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>49</v>
@@ -3616,24 +3602,24 @@
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>60</v>
+        <v>182</v>
       </c>
       <c r="J51" s="3">
-        <v>42</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>226</v>
-      </c>
       <c r="C52" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>49</v>
@@ -3646,13 +3632,13 @@
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3660,10 +3646,10 @@
         <v>94</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>228</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>153</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>36</v>
@@ -3682,7 +3668,7 @@
         <v>230</v>
       </c>
       <c r="J53" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54">
@@ -3690,13 +3676,13 @@
         <v>231</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>37</v>
@@ -3706,27 +3692,27 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="J54" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>234</v>
+        <v>94</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>187</v>
+        <v>233</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>188</v>
+        <v>228</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>37</v>
@@ -3736,27 +3722,27 @@
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="J55" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>94</v>
+        <v>235</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>236</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>153</v>
+        <v>237</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>36</v>
+        <v>205</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>37</v>
@@ -3766,27 +3752,27 @@
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>162</v>
+        <v>239</v>
       </c>
       <c r="J56" s="3">
-        <v>3</v>
+        <v>66</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>238</v>
+        <v>94</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>209</v>
+        <v>119</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>37</v>
@@ -3799,27 +3785,27 @@
         <v>241</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>242</v>
+        <v>182</v>
       </c>
       <c r="J57" s="3">
-        <v>65</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="B58" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="D58" s="3" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
@@ -3829,21 +3815,21 @@
         <v>244</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="J58" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>94</v>
+        <v>245</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>119</v>
@@ -3856,10 +3842,10 @@
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>162</v>
+        <v>46</v>
       </c>
       <c r="J59" s="3">
         <v>3</v>
@@ -3867,100 +3853,102 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>41</v>
+        <v>248</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="J60" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>251</v>
+        <v>197</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>188</v>
+        <v>138</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>46</v>
+        <v>254</v>
       </c>
       <c r="J61" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>149</v>
+        <v>250</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F62" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>257</v>
+      </c>
       <c r="G62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="J62" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>138</v>
@@ -3976,21 +3964,21 @@
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J63" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>138</v>
@@ -4006,21 +3994,21 @@
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="J64" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>138</v>
@@ -4036,21 +4024,21 @@
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>69</v>
       </c>
       <c r="J65" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>138</v>
@@ -4066,54 +4054,54 @@
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="J66" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>152</v>
+        <v>270</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>267</v>
+        <v>204</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>119</v>
+        <v>205</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="J67" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>205</v>
+        <v>148</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>49</v>
@@ -4126,117 +4114,119 @@
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="J68" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>208</v>
+        <v>138</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>209</v>
+        <v>49</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="J69" s="3">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>138</v>
+        <v>250</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="J70" s="3">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>94</v>
+        <v>281</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F71" s="3"/>
+      <c r="F71" s="3" t="s">
+        <v>283</v>
+      </c>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>162</v>
+        <v>65</v>
       </c>
       <c r="J71" s="3">
-        <v>3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>205</v>
+        <v>287</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>37</v>
@@ -4246,113 +4236,111 @@
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>140</v>
+        <v>46</v>
       </c>
       <c r="J72" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>284</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>65</v>
+        <v>163</v>
       </c>
       <c r="J73" s="3">
-        <v>52</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>287</v>
+        <v>152</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>288</v>
+        <v>138</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>46</v>
+        <v>294</v>
       </c>
       <c r="J74" s="3">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>138</v>
+        <v>250</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>166</v>
+        <v>268</v>
       </c>
       <c r="J75" s="3">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>293</v>
+        <v>116</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>164</v>
+        <v>298</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>138</v>
@@ -4368,84 +4356,86 @@
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>295</v>
+        <v>40</v>
       </c>
       <c r="J76" s="3">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>152</v>
+        <v>301</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>267</v>
+        <v>302</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>119</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>140</v>
+        <v>46</v>
       </c>
       <c r="J77" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>195</v>
+        <v>305</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>138</v>
+        <v>306</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F78" s="3"/>
+      <c r="F78" s="3" t="s">
+        <v>307</v>
+      </c>
       <c r="G78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="J78" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>49</v>
@@ -4458,27 +4448,27 @@
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>303</v>
+        <v>69</v>
       </c>
       <c r="J79" s="3">
-        <v>22</v>
+        <v>64</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>305</v>
+        <v>270</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>37</v>
@@ -4488,27 +4478,27 @@
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>265</v>
+        <v>192</v>
       </c>
       <c r="J80" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>116</v>
+        <v>313</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>307</v>
+        <v>273</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>138</v>
+        <v>314</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>42</v>
@@ -4518,72 +4508,70 @@
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="J81" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>119</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>46</v>
+        <v>192</v>
       </c>
       <c r="J82" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>119</v>
+        <v>323</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>316</v>
-      </c>
+      <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="J83" s="3">
         <v>1</v>
@@ -4591,46 +4579,46 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>152</v>
+        <v>326</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>149</v>
+        <v>190</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>69</v>
+        <v>157</v>
       </c>
       <c r="J84" s="3">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>273</v>
+        <v>207</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>188</v>
+        <v>138</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>37</v>
@@ -4640,24 +4628,24 @@
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="J85" s="3">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>323</v>
+        <v>246</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>324</v>
+        <v>190</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>119</v>
@@ -4670,57 +4658,57 @@
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J86" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>328</v>
+        <v>148</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="J87" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>159</v>
+        <v>322</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>160</v>
+        <v>323</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>42</v>
@@ -4730,10 +4718,10 @@
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="J88" s="3">
         <v>0</v>
@@ -4741,13 +4729,13 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>211</v>
+        <v>339</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>49</v>
@@ -4760,27 +4748,27 @@
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="J89" s="3">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>251</v>
+        <v>342</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>42</v>
@@ -4790,27 +4778,27 @@
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="J90" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>149</v>
+        <v>190</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>37</v>
@@ -4820,107 +4808,17 @@
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="J91" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F92" s="3"/>
-      <c r="G92" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="I92" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="J92" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F93" s="3"/>
-      <c r="G93" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="I93" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="J93" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F94" s="3"/>
-      <c r="G94" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J94"/>
+  <autoFilter ref="A1:J91"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5012,9 +4910,6 @@
     <hyperlink ref="H89" r:id="rId88"/>
     <hyperlink ref="H90" r:id="rId89"/>
     <hyperlink ref="H91" r:id="rId90"/>
-    <hyperlink ref="H92" r:id="rId91"/>
-    <hyperlink ref="H93" r:id="rId92"/>
-    <hyperlink ref="H94" r:id="rId93"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5022,8 +4917,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5056,13 +4951,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5070,18 +4965,18 @@
         <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>47</v>
+        <v>174</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5089,18 +4984,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>186</v>
+        <v>94</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5108,18 +5003,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>192</v>
+        <v>255</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>164</v>
+        <v>256</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>149</v>
+        <v>250</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5127,18 +5022,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>193</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>94</v>
+        <v>272</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>216</v>
+        <v>273</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>217</v>
+        <v>148</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5146,18 +5041,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>218</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>226</v>
+        <v>326</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>149</v>
+        <v>190</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5165,18 +5060,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>227</v>
+        <v>327</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>234</v>
+        <v>335</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>187</v>
+        <v>336</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>188</v>
+        <v>322</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5184,144 +5079,11 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G15"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5330,13 +5092,6 @@
     <hyperlink ref="G6" r:id="rId5"/>
     <hyperlink ref="G7" r:id="rId6"/>
     <hyperlink ref="G8" r:id="rId7"/>
-    <hyperlink ref="G9" r:id="rId8"/>
-    <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5350,15 +5105,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B2" s="3">
         <v>16</v>
@@ -5366,7 +5121,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B3" s="3">
         <v>16</v>
@@ -5374,15 +5129,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>352</v>
+        <v>257</v>
       </c>
       <c r="B4" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B5" s="3">
         <v>14</v>
@@ -5390,7 +5145,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B6" s="3">
         <v>10</v>
@@ -5398,7 +5153,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B7" s="3">
         <v>9</v>
@@ -5406,7 +5161,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B8" s="3">
         <v>9</v>
@@ -5414,7 +5169,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B9" s="3">
         <v>8</v>
@@ -5430,7 +5185,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B11" s="3">
         <v>7</v>
@@ -5438,7 +5193,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -5446,7 +5201,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B13" s="3">
         <v>6</v>
@@ -5454,7 +5209,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -5462,7 +5217,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -5470,7 +5225,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5492,28 +5247,28 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="B2" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5521,7 +5276,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5529,7 +5284,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5537,7 +5292,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>89</v>
+        <v>154</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5545,7 +5300,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5569,7 +5324,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5577,7 +5332,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5585,7 +5340,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5593,7 +5348,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5601,7 +5356,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5630,16 +5385,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2">
@@ -5675,13 +5430,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>164</v>
+        <v>62</v>
       </c>
       <c r="C4" s="3">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="D4" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -5689,10 +5444,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="C5" s="3">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="D5" s="3">
         <v>3</v>
@@ -5703,13 +5458,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C6" s="3">
-        <v>7.1</v>
+        <v>6.0</v>
       </c>
       <c r="D6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -5717,13 +5472,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>48</v>
+        <v>152</v>
       </c>
       <c r="C7" s="3">
         <v>6.0</v>
       </c>
       <c r="D7" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -5731,13 +5486,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
       <c r="C8" s="3">
-        <v>6.0</v>
+        <v>3.6</v>
       </c>
       <c r="D8" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -5745,13 +5500,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="C9" s="3">
         <v>3.6</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -5759,7 +5514,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C10" s="3">
         <v>3.6</v>
@@ -5787,7 +5542,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C12" s="3">
         <v>2.8</v>
@@ -5801,7 +5556,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -5829,7 +5584,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5843,7 +5598,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5869,21 +5624,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3">
@@ -5891,10 +5646,10 @@
         <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4">
@@ -5902,10 +5657,10 @@
         <v>42</v>
       </c>
       <c r="B4" s="3">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -5924,7 +5679,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2">
@@ -5932,7 +5687,7 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
@@ -5940,7 +5695,7 @@
         <v>119</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -5948,20 +5703,20 @@
         <v>36</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>160</v>
+        <v>323</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -5977,7 +5732,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -6004,10 +5759,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6019,10 +5774,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6039,7 +5794,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>56</v>
@@ -6048,22 +5803,22 @@
         <v>57</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>300</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3">
@@ -6071,31 +5826,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>379</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>382</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4">
@@ -6103,31 +5858,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>138</v>
+        <v>228</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>391</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5">
@@ -6135,28 +5890,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>69</v>
@@ -6167,31 +5922,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>138</v>
+        <v>394</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F6" s="3">
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>69</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7">
@@ -6199,31 +5954,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>401</v>
+        <v>328</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>402</v>
+        <v>207</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>403</v>
+        <v>138</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F7" s="3">
         <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>405</v>
+        <v>329</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>147</v>
+        <v>398</v>
       </c>
     </row>
     <row r="8">
@@ -6231,31 +5986,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>333</v>
+        <v>399</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>211</v>
+        <v>400</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>138</v>
+        <v>318</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F8" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>334</v>
+        <v>402</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>303</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9">
@@ -6263,31 +6018,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="F9" s="3">
+        <v>88</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="F9" s="3">
-        <v>96</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>410</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="10">
@@ -6295,31 +6050,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="F10" s="3">
+        <v>84</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="H10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="F10" s="3">
-        <v>88</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>417</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>418</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -6327,31 +6082,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>159</v>
+        <v>250</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F11" s="3">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>300</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -6359,31 +6114,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>152</v>
+        <v>420</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>267</v>
+        <v>138</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F12" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>303</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13">
@@ -6391,31 +6146,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="F13" s="3">
+        <v>78</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="F13" s="3">
-        <v>83</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>429</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
@@ -6423,31 +6178,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="F14" s="3">
+        <v>74</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="F14" s="3">
-        <v>80</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>433</v>
-      </c>
       <c r="J14" s="3" t="s">
-        <v>242</v>
+        <v>398</v>
       </c>
     </row>
     <row r="15">
@@ -6455,31 +6210,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="F15" s="3">
+        <v>70</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="F15" s="3">
-        <v>78</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>438</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16">
@@ -6487,31 +6242,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>427</v>
+        <v>384</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="F16" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>303</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17">
@@ -6519,31 +6274,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="F17" s="3">
+        <v>68</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>443</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="F17" s="3">
-        <v>70</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="18">
@@ -6551,31 +6306,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="F18" s="3">
+        <v>61</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="F18" s="3">
-        <v>70</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>448</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>121</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19">
@@ -6583,31 +6338,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="F19" s="3">
+        <v>57</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="H19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="F19" s="3">
-        <v>68</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>453</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>454</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20">
@@ -6615,31 +6370,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="F20" s="3">
+        <v>48</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="F20" s="3">
-        <v>61</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>458</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>65</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21">
@@ -6647,31 +6402,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="F21" s="3">
+        <v>46</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>460</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="F21" s="3">
-        <v>57</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W43.xlsx
+++ b/reports/devops-jobs-israel-2026-W43.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="498">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-23T11:27:54</t>
+    <t xml:space="preserve">2026-10-25T11:13:07</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,12 +57,15 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
+    <t xml:space="preserve">1.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salary disclosure rate %</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.0%</t>
   </si>
   <si>
-    <t xml:space="preserve">Salary disclosure rate %</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maintained by</t>
   </si>
   <si>
@@ -462,6 +465,24 @@
     <t xml:space="preserve">2026-10-15</t>
   </si>
   <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
     <t xml:space="preserve">Deloitte</t>
   </si>
   <si>
@@ -474,6 +495,15 @@
     <t xml:space="preserve">2026-10-14</t>
   </si>
   <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4483375334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-25</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
   </si>
   <si>
@@ -618,6 +648,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4480488912</t>
   </si>
   <si>
+    <t xml:space="preserve">Elementor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-elementor-4482868447</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cellebrite</t>
   </si>
   <si>
@@ -636,12 +675,15 @@
     <t xml:space="preserve">Haifa, Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4480795007</t>
   </si>
   <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4481079700</t>
+  </si>
+  <si>
     <t xml:space="preserve">Paragon</t>
   </si>
   <si>
@@ -651,34 +693,19 @@
     <t xml:space="preserve">2026-08-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4478985380</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pontera</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pontera-4481315450</t>
   </si>
   <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+    <t xml:space="preserve">Personetics</t>
   </si>
   <si>
     <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4480868969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4482494409</t>
@@ -693,15 +720,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-build-lead-cloud-infrastructure-at-a-cutting-edge-cybersecurity-startup-%F0%9F%9A%80-at-pacaya-hr-experts-4479930327</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps &amp; Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Webiks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-reliability-engineer-at-webiks-4482425775</t>
-  </si>
-  <si>
     <t xml:space="preserve">AllCloud</t>
   </si>
   <si>
@@ -720,6 +738,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4482082697</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior Software Engineer, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aiven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-aiven-4426867332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-04</t>
+  </si>
+  <si>
     <t xml:space="preserve">Integress, Inc.</t>
   </si>
   <si>
@@ -747,6 +780,12 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4478276676</t>
   </si>
   <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4482880578</t>
+  </si>
+  <si>
     <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
   </si>
   <si>
@@ -771,12 +810,132 @@
     <t xml:space="preserve">UNIQAI Systems</t>
   </si>
   <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-sre-at-uniqai-systems-4478231249</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-site-reliability-engineer-at-palo-alto-networks-4470801230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-confidential-careers-4476662621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Integrator – SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-integrator-%E2%80%93-sre-at-compie-technologies-4483368453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Integrator SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-integrator-sre-at-moveo-source-4481380188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer - Core Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-core-systems-at-wix-4483368404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-infrastructure-engineer-at-akamai-technologies-4473769865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer -Platform Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-platform-team-at-viz-ai-4437383686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-immunai-4482405033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-jobgether-4480437632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps &amp; Cloud Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-cloud-infrastructure-at-nimble-4450219176</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior Cloud Engineer</t>
   </si>
   <si>
@@ -786,444 +945,354 @@
     <t xml:space="preserve">2026-10-13</t>
   </si>
   <si>
-    <t xml:space="preserve">DevSecOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antidote Health</t>
+    <t xml:space="preserve">Principal DevOps Engineer - AI Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-ai-platforms-at-palo-alto-networks-4471749164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer (Mid-level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-mid-level-at-jobgether-4481691238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guesty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-guesty-4473205757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software developer and DevOps engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysBind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-developer-and-devops-engineer-at-sysbind-4478663562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Engineer (GCP Focus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MyOps by Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-gcp-focus-at-myops-by-yael-group-4478218206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Backend &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Vault</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-backend-devops-engineer-at-the-vault-4481056311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-at-moveo-source-4480775799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-logica-it-4479496280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (37823)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-37823-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4482463663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Administrator (1007969)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-1007969-at-elad-software-systems-4482089049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-confidential-careers-4481088252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4478983773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Administrator - Cloud, Microsoft &amp; Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Octally Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-cloud-microsoft-infrastructure-at-octally-integration-4480045453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer (10296)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bynet Data Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-10296-at-bynet-data-communications-4478972863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Administrator - position no. 1768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBI Investment House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-position-no-1768-at-ibi-investment-house-4478254402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4483376293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">Security</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-antidote-health-4480773737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-site-reliability-engineer-at-palo-alto-networks-4470801230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-confidential-careers-4476662621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Integrator SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-integrator-sre-at-moveo-source-4481380188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-infrastructure-engineer-at-akamai-technologies-4473769865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immunai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-immunai-4482405033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-jobgether-4480437632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps &amp; Cloud Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-cloud-infrastructure-at-nimble-4450219176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guesty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-guesty-4473205757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software developer and DevOps engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysBind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-developer-and-devops-engineer-at-sysbind-4478663562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Engineer (GCP Focus)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MyOps by Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-gcp-focus-at-myops-by-yael-group-4478218206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-at-confidential-careers-4480017132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-at-moveo-source-4480775799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=8264438&amp;gh_jid=8264438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux &amp; HPC Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novocure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirat HaCarmel, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-novocure-4478872342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
   </si>
   <si>
     <t xml:space="preserve">North District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-e2e-solutions-il-4479421024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-logica-it-4479496280</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (37823)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-37823-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4482463663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Administrator (1007969)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-1007969-at-elad-software-systems-4482089049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4478983773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Administrator - Cloud, Microsoft &amp; Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Octally Integration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-cloud-microsoft-infrastructure-at-octally-integration-4480045453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer (10296)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bynet Data Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-10296-at-bynet-data-communications-4478972863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Administrator - position no. 1768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBI Investment House</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-position-no-1768-at-ibi-investment-house-4478254402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INGIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4482435047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=8264438&amp;gh_jid=8264438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux &amp; HPC Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novocure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tirat HaCarmel, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-novocure-4478872342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -1266,6 +1335,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
   </si>
   <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471963869</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
   </si>
   <si>
@@ -1290,21 +1368,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New York City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7995568003</t>
-  </si>
-  <si>
     <t xml:space="preserve">Security Analyst (Student Position)</t>
   </si>
   <si>
@@ -1353,6 +1416,27 @@
     <t xml:space="preserve">2026-09-04</t>
   </si>
   <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-abra-4467537853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Networking, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-medulla-4468207460</t>
+  </si>
+  <si>
     <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
   </si>
   <si>
@@ -1365,43 +1449,16 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Operations Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-compie-technologies-4482446270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
+    <t xml:space="preserve">Linux System Administrator (37866)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-37866-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4482465747</t>
   </si>
   <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
@@ -1419,13 +1476,16 @@
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
     <t xml:space="preserve">Terraform/IaC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1577,7 +1637,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7">
@@ -1585,7 +1645,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -1593,7 +1653,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
@@ -1601,7 +1661,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>859</v>
+        <v>852</v>
       </c>
     </row>
     <row r="10">
@@ -1609,7 +1669,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1625,7 +1685,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -1634,26 +1694,26 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1662,23 +1722,23 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" s="3">
         <v>22</v>
@@ -1697,47 +1757,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="B2" s="3">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="B3" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>407</v>
+        <v>430</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -1750,125 +1810,125 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>463</v>
+        <v>356</v>
       </c>
       <c r="B2" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="B4" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>355</v>
+        <v>484</v>
       </c>
       <c r="B5" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>356</v>
+        <v>384</v>
       </c>
       <c r="B6" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c r="B7" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="B8" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>467</v>
+        <v>486</v>
       </c>
       <c r="B9" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>352</v>
+        <v>379</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>349</v>
+        <v>376</v>
       </c>
       <c r="B13" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>468</v>
+        <v>487</v>
       </c>
       <c r="B15" s="3">
         <v>8</v>
@@ -1876,7 +1936,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>307</v>
+        <v>488</v>
       </c>
       <c r="B16" s="3">
         <v>8</v>
@@ -1898,123 +1958,123 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>469</v>
+        <v>489</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
         <v>22</v>
       </c>
       <c r="C2" s="3">
-        <v>13.1</v>
+        <v>11.2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3">
-        <v>36.7</v>
+        <v>35.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>473</v>
+        <v>493</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.2</v>
+        <v>8.5</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>30.3</v>
+        <v>40.1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>476</v>
+        <v>496</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>15.0</v>
+        <v>17.9</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>477</v>
+        <v>497</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>32.6</v>
+        <v>35.1</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2039,913 +2099,913 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="J3" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J4" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J5" s="3">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="J6" s="3">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J7" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J8" s="3">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J9" s="3">
         <v>66</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="J9" s="3">
-        <v>64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J10" s="3">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J11" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J12" s="3">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J13" s="3">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J14" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J15" s="3">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J16" s="3">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J17" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J18" s="3">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J19" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J20" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J21" s="3">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J22" s="3">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J23" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J24" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J25" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J26" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>94</v>
+        <v>148</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>49</v>
+        <v>151</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="J27" s="3">
-        <v>9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>151</v>
+        <v>95</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>69</v>
+        <v>157</v>
       </c>
       <c r="J28" s="3">
-        <v>64</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -2953,209 +3013,209 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>47</v>
+        <v>161</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="J30" s="3">
-        <v>2</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>161</v>
+        <v>48</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="J31" s="3">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="J32" s="3">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J33" s="3">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>171</v>
+        <v>48</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="J34" s="3">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="J35" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>94</v>
+        <v>181</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>40</v>
+        <v>183</v>
       </c>
       <c r="J36" s="3">
         <v>24</v>
@@ -3163,1056 +3223,1052 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>94</v>
+        <v>184</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>138</v>
+        <v>186</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="J37" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J38" s="3">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="J39" s="3">
-        <v>68</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>188</v>
+        <v>48</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="J40" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>193</v>
+        <v>123</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="J41" s="3">
-        <v>4</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>138</v>
+        <v>200</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>160</v>
+        <v>202</v>
       </c>
       <c r="J42" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>47</v>
+        <v>203</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>200</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>201</v>
+        <v>120</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="J43" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>94</v>
+        <v>206</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>204</v>
+        <v>139</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>205</v>
+        <v>50</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="J44" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>138</v>
+        <v>210</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>209</v>
+        <v>160</v>
       </c>
       <c r="J45" s="3">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>119</v>
+        <v>214</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="J46" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>49</v>
+        <v>151</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="J47" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="J48" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>217</v>
+        <v>95</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>60</v>
+        <v>223</v>
       </c>
       <c r="J49" s="3">
-        <v>43</v>
+        <v>62</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>205</v>
+        <v>50</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>157</v>
+        <v>202</v>
       </c>
       <c r="J50" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>221</v>
+        <v>95</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>148</v>
+        <v>227</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>182</v>
+        <v>88</v>
       </c>
       <c r="J51" s="3">
-        <v>4</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>224</v>
+        <v>95</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>148</v>
+        <v>217</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>49</v>
+        <v>151</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="J52" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>94</v>
+        <v>230</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>228</v>
+        <v>155</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>230</v>
+        <v>192</v>
       </c>
       <c r="J53" s="3">
-        <v>31</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>231</v>
+        <v>95</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>119</v>
+        <v>37</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>192</v>
+        <v>236</v>
       </c>
       <c r="J54" s="3">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>94</v>
+        <v>237</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>233</v>
+        <v>199</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>228</v>
+        <v>200</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="J55" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>205</v>
+        <v>120</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="J56" s="3">
-        <v>66</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>119</v>
+        <v>37</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="J57" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>41</v>
+        <v>246</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="J58" s="3">
-        <v>4</v>
+        <v>68</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>245</v>
+        <v>95</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>46</v>
+        <v>192</v>
       </c>
       <c r="J59" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>248</v>
+        <v>95</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>250</v>
+        <v>155</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="J60" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>252</v>
+        <v>42</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>197</v>
+        <v>255</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>138</v>
+        <v>256</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>254</v>
+        <v>192</v>
       </c>
       <c r="J61" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>257</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>152</v>
+        <v>262</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>138</v>
+        <v>210</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>142</v>
+        <v>192</v>
       </c>
       <c r="J63" s="3">
-        <v>45</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="J64" s="3">
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>207</v>
+        <v>162</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="J65" s="3">
-        <v>64</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>266</v>
+        <v>221</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>268</v>
+        <v>70</v>
       </c>
       <c r="J66" s="3">
-        <v>17</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>204</v>
+        <v>139</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>205</v>
+        <v>50</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>146</v>
+        <v>273</v>
       </c>
       <c r="J67" s="3">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>148</v>
+        <v>217</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>49</v>
+        <v>151</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="J68" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="J69" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>250</v>
+        <v>155</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="J70" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>282</v>
+        <v>178</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>283</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>284</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="J71" s="3">
-        <v>53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4223,238 +4279,238 @@
         <v>286</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>287</v>
+        <v>139</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>46</v>
+        <v>183</v>
       </c>
       <c r="J72" s="3">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>290</v>
-      </c>
       <c r="C73" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J73" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="C74" s="3" t="s">
-        <v>138</v>
+        <v>210</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>293</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>294</v>
+        <v>202</v>
       </c>
       <c r="J74" s="3">
-        <v>50</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="C75" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F75" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="C75" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>297</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>268</v>
+        <v>66</v>
       </c>
       <c r="J75" s="3">
-        <v>17</v>
+        <v>55</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>116</v>
+        <v>298</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>138</v>
+        <v>300</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="J76" s="3">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>302</v>
+        <v>139</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>46</v>
+        <v>173</v>
       </c>
       <c r="J77" s="3">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>305</v>
+        <v>207</v>
       </c>
       <c r="C78" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H78" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="D78" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F78" s="3" t="s">
+      <c r="I78" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="G78" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="J78" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="I79" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="I79" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="J79" s="3">
-        <v>64</v>
+        <v>25</v>
       </c>
     </row>
     <row r="80">
@@ -4462,50 +4518,50 @@
         <v>311</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>270</v>
+        <v>312</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>192</v>
+        <v>273</v>
       </c>
       <c r="J80" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>273</v>
+        <v>299</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>315</v>
@@ -4514,214 +4570,216 @@
         <v>160</v>
       </c>
       <c r="J81" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>317</v>
-      </c>
       <c r="C82" s="3" t="s">
-        <v>318</v>
+        <v>139</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>192</v>
+        <v>41</v>
       </c>
       <c r="J82" s="3">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="B83" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>322</v>
-      </c>
       <c r="D83" s="3" t="s">
-        <v>323</v>
+        <v>120</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="J83" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>157</v>
+        <v>325</v>
       </c>
       <c r="J84" s="3">
-        <v>0</v>
+        <v>86</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="D85" s="3" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F85" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>329</v>
+      </c>
       <c r="G85" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="J85" s="3">
-        <v>43</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>246</v>
+        <v>332</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>160</v>
+        <v>61</v>
       </c>
       <c r="J86" s="3">
-        <v>2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>333</v>
+        <v>164</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="J87" s="3">
-        <v>2</v>
+        <v>66</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>323</v>
+        <v>120</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>42</v>
+        <v>338</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J88" s="3">
         <v>0</v>
@@ -4729,96 +4787,338 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>339</v>
+        <v>281</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>148</v>
+        <v>341</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="J89" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>148</v>
+        <v>345</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>49</v>
+        <v>346</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="J90" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J91" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J92" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J93" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J95" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D96" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="I91" s="3" t="s">
+      <c r="E96" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J96" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J97" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="I98" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="J91" s="3">
-        <v>1</v>
+      <c r="J98" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J99" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J91"/>
+  <autoFilter ref="A1:J99"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4910,6 +5210,14 @@
     <hyperlink ref="H89" r:id="rId88"/>
     <hyperlink ref="H90" r:id="rId89"/>
     <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4917,9 +5225,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="1" max="1" width="41" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -4928,79 +5236,79 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>174</v>
+        <v>48</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>176</v>
+        <v>210</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>177</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>220</v>
@@ -5008,82 +5316,158 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>255</v>
+        <v>95</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>250</v>
+        <v>155</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>325</v>
+        <v>283</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>326</v>
+        <v>178</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>327</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>335</v>
+        <v>288</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>336</v>
+        <v>289</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>322</v>
+        <v>139</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>337</v>
       </c>
+      <c r="C10" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>372</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G12"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5092,6 +5476,10 @@
     <hyperlink ref="G6" r:id="rId5"/>
     <hyperlink ref="G7" r:id="rId6"/>
     <hyperlink ref="G8" r:id="rId7"/>
+    <hyperlink ref="G9" r:id="rId8"/>
+    <hyperlink ref="G10" r:id="rId9"/>
+    <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5105,15 +5493,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>348</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="B2" s="3">
         <v>16</v>
@@ -5121,7 +5509,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="B3" s="3">
         <v>16</v>
@@ -5129,15 +5517,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>257</v>
+        <v>376</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>350</v>
+        <v>377</v>
       </c>
       <c r="B5" s="3">
         <v>14</v>
@@ -5145,7 +5533,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="B6" s="3">
         <v>10</v>
@@ -5153,7 +5541,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>351</v>
+        <v>378</v>
       </c>
       <c r="B7" s="3">
         <v>9</v>
@@ -5161,7 +5549,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>352</v>
+        <v>379</v>
       </c>
       <c r="B8" s="3">
         <v>9</v>
@@ -5169,7 +5557,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>353</v>
+        <v>380</v>
       </c>
       <c r="B9" s="3">
         <v>8</v>
@@ -5177,7 +5565,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B10" s="3">
         <v>7</v>
@@ -5185,7 +5573,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>354</v>
+        <v>381</v>
       </c>
       <c r="B11" s="3">
         <v>7</v>
@@ -5193,7 +5581,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -5201,15 +5589,15 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -5217,7 +5605,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>358</v>
+        <v>384</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -5225,7 +5613,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5244,15 +5632,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="B2" s="3">
         <v>5</v>
@@ -5260,7 +5648,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="3">
         <v>3</v>
@@ -5268,7 +5656,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5276,7 +5664,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5284,7 +5672,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5292,7 +5680,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5300,7 +5688,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5308,7 +5696,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5316,7 +5704,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5324,7 +5712,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5332,7 +5720,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5340,7 +5728,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5348,7 +5736,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>246</v>
+        <v>207</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5356,7 +5744,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5364,7 +5752,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5385,16 +5773,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2">
@@ -5402,7 +5790,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C2" s="3">
         <v>13.4</v>
@@ -5416,7 +5804,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C3" s="3">
         <v>9.2</v>
@@ -5430,7 +5818,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" s="3">
         <v>7.6</v>
@@ -5444,7 +5832,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C5" s="3">
         <v>7.1</v>
@@ -5458,7 +5846,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C6" s="3">
         <v>6.0</v>
@@ -5472,7 +5860,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="C7" s="3">
         <v>6.0</v>
@@ -5486,7 +5874,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C8" s="3">
         <v>3.6</v>
@@ -5500,7 +5888,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C9" s="3">
         <v>3.6</v>
@@ -5514,7 +5902,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="C10" s="3">
         <v>3.6</v>
@@ -5528,7 +5916,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C11" s="3">
         <v>2.9</v>
@@ -5542,7 +5930,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C12" s="3">
         <v>2.8</v>
@@ -5556,7 +5944,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -5570,13 +5958,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>123</v>
+        <v>275</v>
       </c>
       <c r="C14" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -5584,13 +5972,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>189</v>
+        <v>124</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
       </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -5598,7 +5986,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5621,46 +6009,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>364</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>365</v>
+        <v>338</v>
       </c>
       <c r="B2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>366</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="3">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>367</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -5676,31 +6064,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B2" s="3">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
         <v>5</v>
@@ -5708,15 +6096,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>205</v>
+        <v>151</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -5724,7 +6112,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -5732,7 +6120,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -5747,7 +6135,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="44" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -5759,34 +6147,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>369</v>
+        <v>393</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>370</v>
+        <v>394</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>371</v>
+        <v>395</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -5794,31 +6182,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>374</v>
+        <v>398</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>254</v>
+        <v>307</v>
       </c>
     </row>
     <row r="3">
@@ -5826,31 +6214,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>377</v>
+        <v>401</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4">
@@ -5858,31 +6246,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>383</v>
+        <v>407</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>386</v>
+        <v>410</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
@@ -5890,31 +6278,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>391</v>
+        <v>415</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
@@ -5922,31 +6310,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>394</v>
+        <v>418</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="F6" s="3">
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>395</v>
+        <v>419</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>396</v>
+        <v>420</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7">
@@ -5954,31 +6342,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="F7" s="3">
         <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>397</v>
+        <v>421</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>398</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8">
@@ -5986,31 +6374,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>399</v>
+        <v>355</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>400</v>
+        <v>422</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>318</v>
+        <v>423</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="F8" s="3">
         <v>96</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>401</v>
+        <v>424</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>402</v>
+        <v>425</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9">
@@ -6018,31 +6406,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>404</v>
+        <v>427</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>405</v>
+        <v>428</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>406</v>
+        <v>429</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>407</v>
+        <v>430</v>
       </c>
       <c r="F9" s="3">
         <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>409</v>
+        <v>432</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>410</v>
+        <v>433</v>
       </c>
     </row>
     <row r="10">
@@ -6050,31 +6438,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>412</v>
+        <v>435</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="F10" s="3">
         <v>84</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>413</v>
+        <v>436</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>414</v>
+        <v>437</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>254</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
@@ -6082,31 +6470,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>415</v>
+        <v>438</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>416</v>
+        <v>164</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>250</v>
+        <v>155</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="F11" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -6114,31 +6502,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>419</v>
+        <v>441</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>138</v>
+        <v>210</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="F12" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>239</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -6146,31 +6534,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>423</v>
+        <v>445</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>425</v>
+        <v>139</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>373</v>
+        <v>403</v>
       </c>
       <c r="F13" s="3">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>46</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14">
@@ -6178,31 +6566,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="F14" s="3">
         <v>74</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>398</v>
+        <v>310</v>
       </c>
     </row>
     <row r="15">
@@ -6210,31 +6598,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="F15" s="3">
         <v>70</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -6242,31 +6630,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="F16" s="3">
         <v>70</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17">
@@ -6274,31 +6662,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>439</v>
+        <v>460</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="F17" s="3">
         <v>68</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>442</v>
+        <v>463</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>443</v>
+        <v>464</v>
       </c>
     </row>
     <row r="18">
@@ -6306,31 +6694,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>445</v>
+        <v>216</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>138</v>
+        <v>200</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>373</v>
+        <v>403</v>
       </c>
       <c r="F18" s="3">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>65</v>
+        <v>468</v>
       </c>
     </row>
     <row r="19">
@@ -6338,31 +6726,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>449</v>
+        <v>253</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>237</v>
+        <v>469</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="F19" s="3">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>451</v>
+        <v>471</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>93</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20">
@@ -6370,31 +6758,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="F20" s="3">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>192</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21">
@@ -6402,31 +6790,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>457</v>
+        <v>349</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>190</v>
+        <v>477</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="F21" s="3">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>458</v>
+        <v>478</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>460</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
